--- a/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://miamiedu-my.sharepoint.com/personal/famelung_miami_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/tools/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9F49E30-F698-6844-90EF-2086B6435579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9186475-2E83-694B-B13D-3BA00B1F36A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5060" yWindow="660" windowWidth="29500" windowHeight="19160" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>

--- a/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/tools/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9186475-2E83-694B-B13D-3BA00B1F36A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FAB8D8-B8E3-CC4E-99D5-3848DE9A9BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="660" windowWidth="29500" windowHeight="19160" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
+    <workbookView xWindow="3920" yWindow="1900" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11924" uniqueCount="2002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11935" uniqueCount="2013">
   <si>
     <t>Global Volcanism Program - Volcanoes of the World 5.1.0</t>
   </si>
@@ -6042,6 +6042,39 @@
   </si>
   <si>
     <t>Kilauea vertical</t>
+  </si>
+  <si>
+    <t>149.165.154.65/data/HDF5EOS/Lewotolok/miaplpy/overlay.html#/start/-8.2727/123.5110/14.6000?minScale=-1.5&amp;maxScale=1.5&amp;pixelSize=5.5&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Lewotobi/miaplpy/overlay.html#/start/-8.5402/122.7753/13.5@minScale=-1.5&amp;maxScale=1.5</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Kerinci/miaplpy/overlay.html#/start/-1.696/101.270/14.4?minScale=-0.8&amp;maxScale=0.8&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.153.50/start/-8.2450/117.9958/12.5292?flyToDatasetCenter=false&amp;startDataset=S1_asc_083_miaplpy_20141023_20250215_S0836E11794_S0832E11809_S0817E11806_S0820E11792_filtDel4DS&amp;minScale=-3&amp;maxScale=3&amp;startDate=20141023&amp;endDate=20250215&amp;pixelSize=2.1&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Rinjani/miaplpy/overlay.html#/?minScale=-2&amp;maxScale=2</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Agung/miaplpy/overlay.html#/?minScale=-2&amp;maxScale=2</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Bulusan/miaplpy/overlay.html#/?minScale=-2&amp;maxScale=2&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Merapi/miaplpy/overlay.html#/?minScale=-3&amp;maxScale=3&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Mayon/miaplpy/overlay.html#/?minScale=-2&amp;maxScale=2</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Sinabung/miaplpy/overlay.html#/?minScale=-5&amp;maxScale=5&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Semeru/miaplpy/overlay.html#/?minScale=-2&amp;maxScale=2</t>
   </si>
 </sst>
 </file>
@@ -7814,7 +7847,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="b">
         <v>0</v>
       </c>
@@ -7858,7 +7891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="b">
         <v>0</v>
       </c>
@@ -7902,7 +7935,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="b">
         <v>0</v>
       </c>
@@ -7946,7 +7979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="b">
         <v>0</v>
       </c>
@@ -7990,7 +8023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="b">
         <v>0</v>
       </c>
@@ -8034,7 +8067,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="b">
         <v>0</v>
       </c>
@@ -8078,7 +8111,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="b">
         <v>0</v>
       </c>
@@ -8122,7 +8155,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="b">
         <v>0</v>
       </c>
@@ -8166,7 +8199,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="b">
         <v>0</v>
       </c>
@@ -8210,7 +8243,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="b">
         <v>0</v>
       </c>
@@ -8254,7 +8287,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="b">
         <v>0</v>
       </c>
@@ -8298,7 +8331,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="b">
         <v>0</v>
       </c>
@@ -8342,7 +8375,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="b">
         <v>0</v>
       </c>
@@ -8386,7 +8419,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="b">
         <v>0</v>
       </c>
@@ -8430,7 +8463,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="b">
         <v>0</v>
       </c>
@@ -8474,7 +8507,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="b">
         <v>0</v>
       </c>
@@ -8518,7 +8551,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="b">
         <v>0</v>
       </c>
@@ -8562,7 +8595,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="b">
         <v>0</v>
       </c>
@@ -8606,7 +8639,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="b">
         <v>0</v>
       </c>
@@ -8650,7 +8683,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="b">
         <v>0</v>
       </c>
@@ -8694,7 +8727,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="b">
         <v>0</v>
       </c>
@@ -8738,7 +8771,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="b">
         <v>0</v>
       </c>
@@ -8782,7 +8815,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="b">
         <v>0</v>
       </c>
@@ -8826,7 +8859,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="b">
         <v>0</v>
       </c>
@@ -8870,7 +8903,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="b">
         <v>0</v>
       </c>
@@ -8914,7 +8947,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="b">
         <v>0</v>
       </c>
@@ -8958,7 +8991,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="b">
         <v>0</v>
       </c>
@@ -9002,7 +9035,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="b">
         <v>0</v>
       </c>
@@ -9046,7 +9079,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="b">
         <v>0</v>
       </c>
@@ -9090,7 +9123,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="b">
         <v>0</v>
       </c>
@@ -9134,7 +9167,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="b">
         <v>0</v>
       </c>
@@ -9178,7 +9211,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="b">
         <v>0</v>
       </c>
@@ -9222,7 +9255,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="b">
         <v>0</v>
       </c>
@@ -9266,7 +9299,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="b">
         <v>0</v>
       </c>
@@ -9310,7 +9343,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="b">
         <v>0</v>
       </c>
@@ -9354,7 +9387,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="b">
         <v>0</v>
       </c>
@@ -9398,7 +9431,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="b">
         <v>0</v>
       </c>
@@ -9442,7 +9475,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="b">
         <v>0</v>
       </c>
@@ -9486,7 +9519,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="b">
         <v>0</v>
       </c>
@@ -9530,7 +9563,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="b">
         <v>0</v>
       </c>
@@ -9574,7 +9607,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="b">
         <v>0</v>
       </c>
@@ -9618,7 +9651,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="b">
         <v>0</v>
       </c>
@@ -9662,7 +9695,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="b">
         <v>0</v>
       </c>
@@ -9706,7 +9739,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="b">
         <v>0</v>
       </c>
@@ -9750,7 +9783,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="b">
         <v>0</v>
       </c>
@@ -9794,7 +9827,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="b">
         <v>0</v>
       </c>
@@ -9838,7 +9871,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="b">
         <v>0</v>
       </c>
@@ -9882,7 +9915,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="b">
         <v>0</v>
       </c>
@@ -9926,7 +9959,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="b">
         <v>0</v>
       </c>
@@ -9970,7 +10003,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="b">
         <v>0</v>
       </c>
@@ -10014,7 +10047,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="b">
         <v>0</v>
       </c>
@@ -10058,7 +10091,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="b">
         <v>0</v>
       </c>
@@ -10102,7 +10135,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="b">
         <v>0</v>
       </c>
@@ -10146,7 +10179,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="b">
         <v>0</v>
       </c>
@@ -10190,7 +10223,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="b">
         <v>0</v>
       </c>
@@ -10234,7 +10267,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="b">
         <v>0</v>
       </c>
@@ -10278,7 +10311,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="b">
         <v>0</v>
       </c>
@@ -10322,7 +10355,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="b">
         <v>0</v>
       </c>
@@ -10366,7 +10399,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="b">
         <v>0</v>
       </c>
@@ -10410,7 +10443,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="b">
         <v>0</v>
       </c>
@@ -10454,7 +10487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="b">
         <v>0</v>
       </c>
@@ -10498,7 +10531,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="b">
         <v>0</v>
       </c>
@@ -10542,7 +10575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="b">
         <v>0</v>
       </c>
@@ -10586,7 +10619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="b">
         <v>0</v>
       </c>
@@ -10630,7 +10663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="b">
         <v>0</v>
       </c>
@@ -10674,7 +10707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="b">
         <v>0</v>
       </c>
@@ -10718,7 +10751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="b">
         <v>0</v>
       </c>
@@ -10762,7 +10795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="b">
         <v>0</v>
       </c>
@@ -10806,7 +10839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="b">
         <v>0</v>
       </c>
@@ -10850,7 +10883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="b">
         <v>0</v>
       </c>
@@ -10894,7 +10927,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="b">
         <v>0</v>
       </c>
@@ -10938,7 +10971,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="b">
         <v>0</v>
       </c>
@@ -10982,7 +11015,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="b">
         <v>0</v>
       </c>
@@ -11026,7 +11059,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="b">
         <v>0</v>
       </c>
@@ -11070,7 +11103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="b">
         <v>0</v>
       </c>
@@ -11114,7 +11147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="b">
         <v>0</v>
       </c>
@@ -11158,7 +11191,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="b">
         <v>0</v>
       </c>
@@ -11202,7 +11235,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="b">
         <v>0</v>
       </c>
@@ -11246,7 +11279,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="b">
         <v>0</v>
       </c>
@@ -11290,7 +11323,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="b">
         <v>0</v>
       </c>
@@ -11334,7 +11367,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="b">
         <v>0</v>
       </c>
@@ -11378,7 +11411,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="b">
         <v>0</v>
       </c>
@@ -11422,7 +11455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="b">
         <v>0</v>
       </c>
@@ -11466,7 +11499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="b">
         <v>0</v>
       </c>
@@ -11510,7 +11543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="b">
         <v>0</v>
       </c>
@@ -11554,7 +11587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="b">
         <v>0</v>
       </c>
@@ -11598,7 +11631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="b">
         <v>0</v>
       </c>
@@ -11642,7 +11675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="b">
         <v>0</v>
       </c>
@@ -11686,7 +11719,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="b">
         <v>0</v>
       </c>
@@ -11730,7 +11763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="b">
         <v>0</v>
       </c>
@@ -11774,7 +11807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="b">
         <v>0</v>
       </c>
@@ -11818,7 +11851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="b">
         <v>0</v>
       </c>
@@ -11862,7 +11895,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="b">
         <v>0</v>
       </c>
@@ -11906,7 +11939,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="b">
         <v>0</v>
       </c>
@@ -11950,7 +11983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="b">
         <v>0</v>
       </c>
@@ -11994,7 +12027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="b">
         <v>0</v>
       </c>
@@ -12038,7 +12071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="b">
         <v>0</v>
       </c>
@@ -12082,7 +12115,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="b">
         <v>0</v>
       </c>
@@ -12126,7 +12159,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="b">
         <v>0</v>
       </c>
@@ -12170,7 +12203,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="b">
         <v>0</v>
       </c>
@@ -12214,7 +12247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="b">
         <v>0</v>
       </c>
@@ -12258,7 +12291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="b">
         <v>0</v>
       </c>
@@ -12302,7 +12335,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="b">
         <v>0</v>
       </c>
@@ -12346,7 +12379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="b">
         <v>0</v>
       </c>
@@ -12390,7 +12423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="b">
         <v>0</v>
       </c>
@@ -12434,7 +12467,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="b">
         <v>0</v>
       </c>
@@ -12478,7 +12511,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="b">
         <v>0</v>
       </c>
@@ -12522,7 +12555,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="b">
         <v>0</v>
       </c>
@@ -12566,7 +12599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="b">
         <v>0</v>
       </c>
@@ -12610,7 +12643,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="b">
         <v>0</v>
       </c>
@@ -12654,7 +12687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="b">
         <v>0</v>
       </c>
@@ -12698,7 +12731,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="b">
         <v>0</v>
       </c>
@@ -12742,7 +12775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="b">
         <v>0</v>
       </c>
@@ -12786,7 +12819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="b">
         <v>0</v>
       </c>
@@ -12830,7 +12863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="b">
         <v>0</v>
       </c>
@@ -12874,7 +12907,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="b">
         <v>0</v>
       </c>
@@ -12918,7 +12951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="b">
         <v>0</v>
       </c>
@@ -12962,7 +12995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="b">
         <v>0</v>
       </c>
@@ -13006,7 +13039,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="b">
         <v>0</v>
       </c>
@@ -13050,7 +13083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="b">
         <v>0</v>
       </c>
@@ -13094,7 +13127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="b">
         <v>0</v>
       </c>
@@ -13138,7 +13171,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="152" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="b">
         <v>0</v>
       </c>
@@ -13182,7 +13215,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="b">
         <v>0</v>
       </c>
@@ -13226,7 +13259,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="b">
         <v>0</v>
       </c>
@@ -13270,7 +13303,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="b">
         <v>0</v>
       </c>
@@ -13314,7 +13347,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="b">
         <v>0</v>
       </c>
@@ -13358,7 +13391,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="b">
         <v>0</v>
       </c>
@@ -13402,7 +13435,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="b">
         <v>0</v>
       </c>
@@ -13446,7 +13479,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="b">
         <v>0</v>
       </c>
@@ -13490,7 +13523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="b">
         <v>0</v>
       </c>
@@ -13534,7 +13567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="b">
         <v>0</v>
       </c>
@@ -13578,7 +13611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="b">
         <v>0</v>
       </c>
@@ -13622,7 +13655,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="b">
         <v>0</v>
       </c>
@@ -13666,7 +13699,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="b">
         <v>0</v>
       </c>
@@ -13710,7 +13743,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="b">
         <v>0</v>
       </c>
@@ -13754,7 +13787,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="b">
         <v>0</v>
       </c>
@@ -13798,7 +13831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="b">
         <v>0</v>
       </c>
@@ -13842,7 +13875,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="b">
         <v>0</v>
       </c>
@@ -13886,7 +13919,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="b">
         <v>0</v>
       </c>
@@ -13930,7 +13963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="b">
         <v>0</v>
       </c>
@@ -13974,7 +14007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="b">
         <v>0</v>
       </c>
@@ -14018,7 +14051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="b">
         <v>0</v>
       </c>
@@ -14062,7 +14095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="b">
         <v>0</v>
       </c>
@@ -14106,7 +14139,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="b">
         <v>0</v>
       </c>
@@ -14150,7 +14183,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="b">
         <v>0</v>
       </c>
@@ -14194,7 +14227,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="b">
         <v>0</v>
       </c>
@@ -14238,7 +14271,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="177" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="b">
         <v>0</v>
       </c>
@@ -14282,7 +14315,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="178" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="b">
         <v>0</v>
       </c>
@@ -14326,7 +14359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="179" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="b">
         <v>0</v>
       </c>
@@ -14370,7 +14403,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="b">
         <v>0</v>
       </c>
@@ -14414,7 +14447,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="b">
         <v>0</v>
       </c>
@@ -14458,7 +14491,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="b">
         <v>0</v>
       </c>
@@ -14502,7 +14535,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="b">
         <v>0</v>
       </c>
@@ -14546,7 +14579,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="184" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="b">
         <v>0</v>
       </c>
@@ -14590,7 +14623,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="185" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="b">
         <v>0</v>
       </c>
@@ -14634,7 +14667,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="186" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="b">
         <v>0</v>
       </c>
@@ -14678,7 +14711,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="187" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="b">
         <v>0</v>
       </c>
@@ -14722,7 +14755,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="b">
         <v>0</v>
       </c>
@@ -14766,7 +14799,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="b">
         <v>0</v>
       </c>
@@ -14810,7 +14843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="190" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="b">
         <v>0</v>
       </c>
@@ -14854,7 +14887,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="191" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="b">
         <v>0</v>
       </c>
@@ -14898,7 +14931,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="192" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="b">
         <v>0</v>
       </c>
@@ -14942,7 +14975,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="193" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="b">
         <v>0</v>
       </c>
@@ -14986,7 +15019,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="194" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="b">
         <v>0</v>
       </c>
@@ -15030,7 +15063,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="195" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="b">
         <v>0</v>
       </c>
@@ -15074,7 +15107,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="196" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="b">
         <v>0</v>
       </c>
@@ -15118,7 +15151,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="197" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="b">
         <v>0</v>
       </c>
@@ -15162,7 +15195,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="198" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="b">
         <v>0</v>
       </c>
@@ -15206,7 +15239,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="199" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="b">
         <v>0</v>
       </c>
@@ -15250,7 +15283,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="200" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="b">
         <v>0</v>
       </c>
@@ -15294,7 +15327,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="b">
         <v>0</v>
       </c>
@@ -15338,7 +15371,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="202" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="b">
         <v>0</v>
       </c>
@@ -15382,7 +15415,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="b">
         <v>0</v>
       </c>
@@ -15426,7 +15459,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="204" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="b">
         <v>0</v>
       </c>
@@ -15470,7 +15503,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="205" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="b">
         <v>0</v>
       </c>
@@ -15514,7 +15547,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="b">
         <v>0</v>
       </c>
@@ -15558,7 +15591,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="207" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="b">
         <v>0</v>
       </c>
@@ -15602,7 +15635,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="208" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="b">
         <v>0</v>
       </c>
@@ -15646,7 +15679,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="209" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="b">
         <v>0</v>
       </c>
@@ -15690,7 +15723,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="210" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="b">
         <v>0</v>
       </c>
@@ -15734,7 +15767,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="211" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="b">
         <v>0</v>
       </c>
@@ -15778,7 +15811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="b">
         <v>0</v>
       </c>
@@ -15822,7 +15855,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="b">
         <v>0</v>
       </c>
@@ -15866,7 +15899,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="214" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="b">
         <v>0</v>
       </c>
@@ -15910,7 +15943,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="b">
         <v>0</v>
       </c>
@@ -15954,7 +15987,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="b">
         <v>0</v>
       </c>
@@ -15998,7 +16031,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="217" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="b">
         <v>0</v>
       </c>
@@ -16042,7 +16075,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="b">
         <v>0</v>
       </c>
@@ -16086,7 +16119,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="b">
         <v>0</v>
       </c>
@@ -16130,7 +16163,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="220" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="b">
         <v>0</v>
       </c>
@@ -16174,7 +16207,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="b">
         <v>0</v>
       </c>
@@ -16218,7 +16251,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="b">
         <v>0</v>
       </c>
@@ -16262,7 +16295,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="b">
         <v>0</v>
       </c>
@@ -16306,7 +16339,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="224" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="b">
         <v>0</v>
       </c>
@@ -16350,7 +16383,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="225" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="b">
         <v>0</v>
       </c>
@@ -16394,7 +16427,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="226" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="b">
         <v>0</v>
       </c>
@@ -16438,7 +16471,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="227" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="b">
         <v>0</v>
       </c>
@@ -16482,7 +16515,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="228" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="b">
         <v>0</v>
       </c>
@@ -16526,7 +16559,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="b">
         <v>0</v>
       </c>
@@ -16570,7 +16603,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="b">
         <v>0</v>
       </c>
@@ -16614,7 +16647,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="231" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="b">
         <v>0</v>
       </c>
@@ -16658,7 +16691,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="232" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="b">
         <v>0</v>
       </c>
@@ -16702,7 +16735,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="233" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="b">
         <v>0</v>
       </c>
@@ -16746,7 +16779,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="234" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="b">
         <v>0</v>
       </c>
@@ -16790,7 +16823,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="b">
         <v>0</v>
       </c>
@@ -16834,7 +16867,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="b">
         <v>0</v>
       </c>
@@ -16878,7 +16911,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="b">
         <v>0</v>
       </c>
@@ -16922,7 +16955,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="b">
         <v>0</v>
       </c>
@@ -16966,7 +16999,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="b">
         <v>0</v>
       </c>
@@ -17010,7 +17043,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="b">
         <v>0</v>
       </c>
@@ -17054,7 +17087,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="b">
         <v>0</v>
       </c>
@@ -17098,7 +17131,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="242" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="b">
         <v>0</v>
       </c>
@@ -17142,7 +17175,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="b">
         <v>0</v>
       </c>
@@ -17186,7 +17219,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="244" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="b">
         <v>0</v>
       </c>
@@ -17230,7 +17263,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="b">
         <v>0</v>
       </c>
@@ -17274,7 +17307,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="246" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="b">
         <v>0</v>
       </c>
@@ -17318,7 +17351,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="b">
         <v>0</v>
       </c>
@@ -17362,7 +17395,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="b">
         <v>0</v>
       </c>
@@ -17406,7 +17439,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="b">
         <v>0</v>
       </c>
@@ -17450,7 +17483,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="b">
         <v>0</v>
       </c>
@@ -17494,7 +17527,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="b">
         <v>0</v>
       </c>
@@ -17538,7 +17571,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="b">
         <v>0</v>
       </c>
@@ -17582,7 +17615,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="b">
         <v>0</v>
       </c>
@@ -17626,7 +17659,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="b">
         <v>0</v>
       </c>
@@ -17670,7 +17703,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="b">
         <v>0</v>
       </c>
@@ -17714,7 +17747,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="256" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="b">
         <v>0</v>
       </c>
@@ -17758,7 +17791,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="257" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="b">
         <v>0</v>
       </c>
@@ -17802,7 +17835,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="258" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="b">
         <v>0</v>
       </c>
@@ -17846,7 +17879,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="259" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="b">
         <v>0</v>
       </c>
@@ -17890,7 +17923,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="b">
         <v>0</v>
       </c>
@@ -17934,7 +17967,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="b">
         <v>0</v>
       </c>
@@ -17978,7 +18011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="b">
         <v>0</v>
       </c>
@@ -18022,7 +18055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="b">
         <v>0</v>
       </c>
@@ -18066,7 +18099,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="b">
         <v>0</v>
       </c>
@@ -18110,7 +18143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="b">
         <v>0</v>
       </c>
@@ -18154,7 +18187,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="b">
         <v>0</v>
       </c>
@@ -18198,7 +18231,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="b">
         <v>0</v>
       </c>
@@ -18242,7 +18275,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="268" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="b">
         <v>0</v>
       </c>
@@ -18286,7 +18319,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="269" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="b">
         <v>0</v>
       </c>
@@ -18330,7 +18363,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="b">
         <v>0</v>
       </c>
@@ -18374,7 +18407,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="b">
         <v>0</v>
       </c>
@@ -18418,7 +18451,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="272" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="b">
         <v>0</v>
       </c>
@@ -18462,7 +18495,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="b">
         <v>0</v>
       </c>
@@ -18506,7 +18539,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="b">
         <v>0</v>
       </c>
@@ -18550,7 +18583,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="b">
         <v>0</v>
       </c>
@@ -18594,7 +18627,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="b">
         <v>0</v>
       </c>
@@ -18638,7 +18671,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="b">
         <v>0</v>
       </c>
@@ -18682,7 +18715,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="b">
         <v>0</v>
       </c>
@@ -18726,7 +18759,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="b">
         <v>0</v>
       </c>
@@ -18770,7 +18803,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="280" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="b">
         <v>0</v>
       </c>
@@ -18814,7 +18847,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="b">
         <v>0</v>
       </c>
@@ -18858,7 +18891,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="b">
         <v>0</v>
       </c>
@@ -18902,7 +18935,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="b">
         <v>0</v>
       </c>
@@ -18946,7 +18979,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="284" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="b">
         <v>0</v>
       </c>
@@ -18990,7 +19023,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="285" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="b">
         <v>0</v>
       </c>
@@ -19034,7 +19067,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="286" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="b">
         <v>0</v>
       </c>
@@ -19078,7 +19111,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="287" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="b">
         <v>0</v>
       </c>
@@ -19122,7 +19155,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="288" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="b">
         <v>0</v>
       </c>
@@ -19166,7 +19199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="289" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="b">
         <v>0</v>
       </c>
@@ -19210,7 +19243,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="290" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="b">
         <v>0</v>
       </c>
@@ -19254,7 +19287,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="291" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="b">
         <v>0</v>
       </c>
@@ -19298,7 +19331,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="292" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="b">
         <v>0</v>
       </c>
@@ -19342,7 +19375,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="293" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="b">
         <v>0</v>
       </c>
@@ -19386,7 +19419,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="294" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="b">
         <v>0</v>
       </c>
@@ -19430,7 +19463,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="295" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="b">
         <v>0</v>
       </c>
@@ -19474,7 +19507,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="296" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="b">
         <v>0</v>
       </c>
@@ -19518,7 +19551,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="297" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="b">
         <v>0</v>
       </c>
@@ -19562,7 +19595,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="298" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="b">
         <v>0</v>
       </c>
@@ -19606,7 +19639,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="299" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="b">
         <v>0</v>
       </c>
@@ -19650,7 +19683,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="300" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="b">
         <v>0</v>
       </c>
@@ -19694,7 +19727,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="301" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="b">
         <v>0</v>
       </c>
@@ -19738,7 +19771,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="302" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="b">
         <v>0</v>
       </c>
@@ -19782,7 +19815,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="303" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="b">
         <v>0</v>
       </c>
@@ -19826,7 +19859,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="304" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="b">
         <v>0</v>
       </c>
@@ -19870,7 +19903,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="305" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="b">
         <v>0</v>
       </c>
@@ -19914,7 +19947,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="306" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="b">
         <v>0</v>
       </c>
@@ -19958,7 +19991,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="307" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="b">
         <v>0</v>
       </c>
@@ -20002,7 +20035,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="308" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="b">
         <v>0</v>
       </c>
@@ -20046,7 +20079,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="309" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="b">
         <v>0</v>
       </c>
@@ -20090,7 +20123,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="310" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="b">
         <v>0</v>
       </c>
@@ -20134,7 +20167,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="311" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="b">
         <v>0</v>
       </c>
@@ -20178,7 +20211,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="312" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="b">
         <v>0</v>
       </c>
@@ -20222,7 +20255,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="313" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="b">
         <v>0</v>
       </c>
@@ -20266,7 +20299,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="314" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="b">
         <v>0</v>
       </c>
@@ -20310,7 +20343,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="315" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="b">
         <v>0</v>
       </c>
@@ -20354,7 +20387,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="316" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="b">
         <v>0</v>
       </c>
@@ -20398,7 +20431,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="317" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="b">
         <v>0</v>
       </c>
@@ -20442,7 +20475,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="318" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="b">
         <v>0</v>
       </c>
@@ -20486,7 +20519,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="319" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="b">
         <v>0</v>
       </c>
@@ -20530,7 +20563,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="320" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20607,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="321" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="b">
         <v>0</v>
       </c>
@@ -20618,7 +20651,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="322" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="b">
         <v>0</v>
       </c>
@@ -20662,7 +20695,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="323" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="b">
         <v>0</v>
       </c>
@@ -20706,7 +20739,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="324" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="b">
         <v>0</v>
       </c>
@@ -20750,7 +20783,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="325" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="b">
         <v>0</v>
       </c>
@@ -20794,7 +20827,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="326" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="b">
         <v>0</v>
       </c>
@@ -20838,7 +20871,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="327" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="b">
         <v>0</v>
       </c>
@@ -20882,7 +20915,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="328" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="b">
         <v>0</v>
       </c>
@@ -20926,7 +20959,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="329" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="b">
         <v>0</v>
       </c>
@@ -20970,7 +21003,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="330" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="b">
         <v>0</v>
       </c>
@@ -21014,7 +21047,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="331" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="b">
         <v>0</v>
       </c>
@@ -21058,7 +21091,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="332" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="b">
         <v>0</v>
       </c>
@@ -21102,7 +21135,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="333" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="b">
         <v>0</v>
       </c>
@@ -21146,7 +21179,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="334" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="b">
         <v>0</v>
       </c>
@@ -21190,7 +21223,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="335" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="b">
         <v>0</v>
       </c>
@@ -21234,7 +21267,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="336" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="b">
         <v>0</v>
       </c>
@@ -21278,7 +21311,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="337" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="b">
         <v>0</v>
       </c>
@@ -21322,9 +21355,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="338" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A338" s="1" t="b">
-        <v>0</v>
+    <row r="338" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="6" t="s">
+        <v>2011</v>
       </c>
       <c r="B338" s="3">
         <v>261080</v>
@@ -21366,7 +21399,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="339" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="b">
         <v>0</v>
       </c>
@@ -21410,7 +21443,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="340" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="b">
         <v>0</v>
       </c>
@@ -21454,7 +21487,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="341" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="b">
         <v>0</v>
       </c>
@@ -21498,7 +21531,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="342" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="b">
         <v>0</v>
       </c>
@@ -21542,7 +21575,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="343" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="b">
         <v>0</v>
       </c>
@@ -21586,7 +21619,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="344" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="b">
         <v>0</v>
       </c>
@@ -21630,7 +21663,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="345" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="b">
         <v>0</v>
       </c>
@@ -21674,7 +21707,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="346" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="b">
         <v>0</v>
       </c>
@@ -21718,7 +21751,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="347" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="b">
         <v>0</v>
       </c>
@@ -21762,7 +21795,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="348" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="b">
         <v>0</v>
       </c>
@@ -21806,9 +21839,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="349" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="1" t="b">
-        <v>0</v>
+    <row r="349" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="6" t="s">
+        <v>2004</v>
       </c>
       <c r="B349" s="3">
         <v>261170</v>
@@ -21850,7 +21883,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="350" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="b">
         <v>0</v>
       </c>
@@ -21894,7 +21927,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="351" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="b">
         <v>0</v>
       </c>
@@ -21938,7 +21971,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="352" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="b">
         <v>0</v>
       </c>
@@ -21982,7 +22015,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="353" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="b">
         <v>0</v>
       </c>
@@ -22026,7 +22059,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="354" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="b">
         <v>0</v>
       </c>
@@ -22070,7 +22103,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="355" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="b">
         <v>0</v>
       </c>
@@ -22114,7 +22147,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="356" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="b">
         <v>0</v>
       </c>
@@ -22158,7 +22191,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="357" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="b">
         <v>0</v>
       </c>
@@ -22202,7 +22235,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="358" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="b">
         <v>0</v>
       </c>
@@ -22246,7 +22279,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="359" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="b">
         <v>0</v>
       </c>
@@ -22290,7 +22323,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="360" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="b">
         <v>0</v>
       </c>
@@ -22334,7 +22367,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="361" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="b">
         <v>0</v>
       </c>
@@ -22378,7 +22411,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="362" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="b">
         <v>0</v>
       </c>
@@ -22422,7 +22455,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="363" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="b">
         <v>0</v>
       </c>
@@ -22466,7 +22499,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="364" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="b">
         <v>0</v>
       </c>
@@ -22510,7 +22543,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="365" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="b">
         <v>0</v>
       </c>
@@ -22554,7 +22587,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="366" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="b">
         <v>0</v>
       </c>
@@ -22598,7 +22631,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="367" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="b">
         <v>0</v>
       </c>
@@ -22642,7 +22675,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="368" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="b">
         <v>0</v>
       </c>
@@ -22686,7 +22719,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="369" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="b">
         <v>0</v>
       </c>
@@ -22730,7 +22763,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="370" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="b">
         <v>0</v>
       </c>
@@ -22774,7 +22807,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="371" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="b">
         <v>0</v>
       </c>
@@ -22818,7 +22851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="372" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="b">
         <v>0</v>
       </c>
@@ -22862,7 +22895,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="373" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="b">
         <v>0</v>
       </c>
@@ -22906,7 +22939,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="374" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="b">
         <v>0</v>
       </c>
@@ -22950,7 +22983,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="375" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="b">
         <v>0</v>
       </c>
@@ -22994,7 +23027,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="376" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="b">
         <v>0</v>
       </c>
@@ -23038,7 +23071,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="377" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="b">
         <v>0</v>
       </c>
@@ -23126,7 +23159,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="379" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="b">
         <v>0</v>
       </c>
@@ -23170,7 +23203,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="380" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="b">
         <v>0</v>
       </c>
@@ -23214,7 +23247,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="381" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="b">
         <v>0</v>
       </c>
@@ -23303,8 +23336,8 @@
       </c>
     </row>
     <row r="383" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A383" s="1" t="b">
-        <v>0</v>
+      <c r="A383" s="6" t="s">
+        <v>2009</v>
       </c>
       <c r="B383" s="3">
         <v>263250</v>
@@ -23391,8 +23424,8 @@
       </c>
     </row>
     <row r="385" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A385" s="1" t="b">
-        <v>0</v>
+      <c r="A385" s="6" t="s">
+        <v>2012</v>
       </c>
       <c r="B385" s="3">
         <v>263300</v>
@@ -23654,7 +23687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="391" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="b">
         <v>0</v>
       </c>
@@ -23698,7 +23731,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="392" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="b">
         <v>0</v>
       </c>
@@ -23787,8 +23820,8 @@
       </c>
     </row>
     <row r="394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A394" s="1" t="b">
-        <v>0</v>
+      <c r="A394" s="6" t="s">
+        <v>2007</v>
       </c>
       <c r="B394" s="3">
         <v>264020</v>
@@ -23831,8 +23864,8 @@
       </c>
     </row>
     <row r="395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A395" s="1" t="b">
-        <v>0</v>
+      <c r="A395" s="6" t="s">
+        <v>2006</v>
       </c>
       <c r="B395" s="3">
         <v>264030</v>
@@ -23875,8 +23908,8 @@
       </c>
     </row>
     <row r="396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A396" s="1" t="b">
-        <v>0</v>
+      <c r="A396" s="6" t="s">
+        <v>2005</v>
       </c>
       <c r="B396" s="3">
         <v>264040</v>
@@ -23963,8 +23996,8 @@
       </c>
     </row>
     <row r="398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A398" s="1" t="b">
-        <v>0</v>
+      <c r="A398" s="6" t="s">
+        <v>2003</v>
       </c>
       <c r="B398" s="3">
         <v>264180</v>
@@ -24006,7 +24039,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="399" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="b">
         <v>0</v>
       </c>
@@ -24050,7 +24083,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="400" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="b">
         <v>0</v>
       </c>
@@ -24094,9 +24127,9 @@
         <v>463</v>
       </c>
     </row>
-    <row r="401" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A401" s="1" t="b">
-        <v>0</v>
+    <row r="401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A401" s="6" t="s">
+        <v>2002</v>
       </c>
       <c r="B401" s="3">
         <v>264230</v>
@@ -24138,7 +24171,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="402" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="b">
         <v>0</v>
       </c>
@@ -24314,7 +24347,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="406" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="b">
         <v>0</v>
       </c>
@@ -24358,7 +24391,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="407" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="b">
         <v>0</v>
       </c>
@@ -24490,7 +24523,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="410" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="b">
         <v>0</v>
       </c>
@@ -24578,7 +24611,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="412" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="b">
         <v>0</v>
       </c>
@@ -24622,7 +24655,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="413" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="b">
         <v>0</v>
       </c>
@@ -24710,7 +24743,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="415" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="b">
         <v>0</v>
       </c>
@@ -24754,7 +24787,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="416" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="b">
         <v>0</v>
       </c>
@@ -24798,7 +24831,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="417" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="b">
         <v>0</v>
       </c>
@@ -24842,7 +24875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="418" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="b">
         <v>0</v>
       </c>
@@ -24974,7 +25007,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="421" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="b">
         <v>0</v>
       </c>
@@ -25150,7 +25183,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="425" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="b">
         <v>0</v>
       </c>
@@ -25238,7 +25271,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="427" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="b">
         <v>0</v>
       </c>
@@ -25282,7 +25315,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="428" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="b">
         <v>0</v>
       </c>
@@ -25326,7 +25359,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="429" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="b">
         <v>0</v>
       </c>
@@ -25370,7 +25403,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="430" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="b">
         <v>0</v>
       </c>
@@ -25458,7 +25491,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="432" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="b">
         <v>0</v>
       </c>
@@ -25502,7 +25535,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="433" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="b">
         <v>0</v>
       </c>
@@ -25546,7 +25579,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="434" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="b">
         <v>0</v>
       </c>
@@ -25590,7 +25623,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="435" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="b">
         <v>0</v>
       </c>
@@ -25634,7 +25667,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="436" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="b">
         <v>0</v>
       </c>
@@ -25678,7 +25711,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="437" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="b">
         <v>0</v>
       </c>
@@ -25722,7 +25755,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="438" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="b">
         <v>0</v>
       </c>
@@ -25766,7 +25799,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="439" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="b">
         <v>0</v>
       </c>
@@ -25810,7 +25843,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="440" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="b">
         <v>0</v>
       </c>
@@ -25854,7 +25887,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="441" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="b">
         <v>0</v>
       </c>
@@ -25898,7 +25931,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="442" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="b">
         <v>0</v>
       </c>
@@ -25942,7 +25975,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="443" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="b">
         <v>0</v>
       </c>
@@ -25986,7 +26019,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="444" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="b">
         <v>0</v>
       </c>
@@ -26030,7 +26063,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="445" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="b">
         <v>0</v>
       </c>
@@ -26074,7 +26107,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="446" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="b">
         <v>0</v>
       </c>
@@ -26118,7 +26151,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="447" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="b">
         <v>0</v>
       </c>
@@ -26162,7 +26195,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="448" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="b">
         <v>0</v>
       </c>
@@ -26206,7 +26239,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="449" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="b">
         <v>0</v>
       </c>
@@ -26250,7 +26283,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="450" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="b">
         <v>0</v>
       </c>
@@ -26294,7 +26327,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="451" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="b">
         <v>0</v>
       </c>
@@ -26338,7 +26371,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="452" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="b">
         <v>0</v>
       </c>
@@ -26382,7 +26415,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="453" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="b">
         <v>0</v>
       </c>
@@ -26426,7 +26459,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="454" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="b">
         <v>0</v>
       </c>
@@ -26470,7 +26503,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="455" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="b">
         <v>0</v>
       </c>
@@ -26514,7 +26547,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="456" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="b">
         <v>0</v>
       </c>
@@ -26558,9 +26591,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="457" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A457" s="1" t="b">
-        <v>0</v>
+    <row r="457" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A457" s="6" t="s">
+        <v>2008</v>
       </c>
       <c r="B457" s="3">
         <v>273010</v>
@@ -26602,7 +26635,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="458" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="b">
         <v>0</v>
       </c>
@@ -26646,9 +26679,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="459" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A459" s="1" t="b">
-        <v>0</v>
+    <row r="459" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A459" s="6" t="s">
+        <v>2010</v>
       </c>
       <c r="B459" s="3">
         <v>273030</v>
@@ -26690,7 +26723,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="460" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="b">
         <v>0</v>
       </c>
@@ -26734,7 +26767,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="461" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="b">
         <v>0</v>
       </c>
@@ -26778,7 +26811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="462" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="b">
         <v>0</v>
       </c>
@@ -26822,7 +26855,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="463" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="b">
         <v>0</v>
       </c>
@@ -66014,6 +66047,17 @@
     <hyperlink ref="A905" r:id="rId1343" xr:uid="{6F69D3AA-AEA7-1142-9894-0755A8D901C0}"/>
     <hyperlink ref="B905" r:id="rId1344" display="https://volcano.si.edu/volcano.cfm?vn=332010" xr:uid="{49AFC9C8-A551-3948-9FE3-436253A7BFE1}"/>
     <hyperlink ref="A904" r:id="rId1345" display="https://insarmaps.miami.edu/start/19.4032/-155.2273/10.9779?flyToDatasetCenter=false&amp;startDataset=S1_vert_087_124_mintpy_20180902_XXXXXXXX_N1978W15586_N1978W15473_N1912W15473_N1912W15586&amp;pointLat=19.39940&amp;pointLon=-155.27805&amp;minScale=-20&amp;maxScale=20&amp;startDate=20180902&amp;endDate=20260228&amp;pixelSize=3.3" xr:uid="{06950C1A-A714-B24B-BABA-AC6C3B02267A}"/>
+    <hyperlink ref="A401" r:id="rId1346" display="http://149.165.154.65/data/HDF5EOS/Lewotolok/miaiply" xr:uid="{73831688-CC6A-3643-8C99-1F23A35EC407}"/>
+    <hyperlink ref="A398" r:id="rId1347" location="/start/-8.5402/122.7753/13.5@minScale=-1.5&amp;maxScale=1.5" xr:uid="{BA612BF8-6BAA-CB4E-9663-BCA3638E8A15}"/>
+    <hyperlink ref="A349" r:id="rId1348" location="/start/-1.696/101.270/14.4?minScale=-0.8&amp;maxScale=0.8&amp;background=satellite" xr:uid="{38CAB67B-7C95-0943-9B63-ECFFB44BCC04}"/>
+    <hyperlink ref="A396" r:id="rId1349" display="http://149.165.153.50/start/-8.2450/117.9958/12.5292?flyToDatasetCenter=false&amp;startDataset=S1_asc_083_miaplpy_20141023_20250215_S0836E11794_S0832E11809_S0817E11806_S0820E11792_filtDel4DS&amp;minScale=-3&amp;maxScale=3&amp;startDate=20141023&amp;endDate=20250215&amp;pixelSize=2.1&amp;background=satellite" xr:uid="{074096C7-BC89-3546-B9E6-FF4457770D48}"/>
+    <hyperlink ref="A395" r:id="rId1350" location="/?minScale=-2&amp;maxScale=2" xr:uid="{F3B432C2-873D-E449-9307-C22F5E984A00}"/>
+    <hyperlink ref="A394" r:id="rId1351" location="/?minScale=-2&amp;maxScale=2" xr:uid="{9CDE4C14-CEA9-B04D-B9EC-D9486F8733A6}"/>
+    <hyperlink ref="A457" r:id="rId1352" location="/?minScale=-2&amp;maxScale=2&amp;background=satellite" xr:uid="{A0F91AE9-8E31-0D4A-96E8-81CCF82F1A52}"/>
+    <hyperlink ref="A383" r:id="rId1353" location="/?minScale=-3&amp;maxScale=3&amp;background=satellite" xr:uid="{D1B95BF0-B5D7-D447-B1AA-4DF1E4361020}"/>
+    <hyperlink ref="A459" r:id="rId1354" location="/?minScale=-2&amp;maxScale=2" xr:uid="{979264A1-1EDE-9941-B821-5E19B7EC19AE}"/>
+    <hyperlink ref="A338" r:id="rId1355" location="/?minScale=-5&amp;maxScale=5&amp;background=satellite" xr:uid="{B59A7083-C90A-3442-B482-B97C567E58E3}"/>
+    <hyperlink ref="A385" r:id="rId1356" location="/?minScale=-2&amp;maxScale=2" xr:uid="{ADDB8508-D649-ED42-98CC-A33FD8E3B0DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/tools/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FAB8D8-B8E3-CC4E-99D5-3848DE9A9BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEB435F-95A0-F841-9DAF-3A76E8D65916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3920" yWindow="1900" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
@@ -6044,9 +6044,6 @@
     <t>Kilauea vertical</t>
   </si>
   <si>
-    <t>149.165.154.65/data/HDF5EOS/Lewotolok/miaplpy/overlay.html#/start/-8.2727/123.5110/14.6000?minScale=-1.5&amp;maxScale=1.5&amp;pixelSize=5.5&amp;background=satellite</t>
-  </si>
-  <si>
     <t>http://149.165.154.65/data/HDF5EOS/Lewotobi/miaplpy/overlay.html#/start/-8.5402/122.7753/13.5@minScale=-1.5&amp;maxScale=1.5</t>
   </si>
   <si>
@@ -6075,6 +6072,9 @@
   </si>
   <si>
     <t>http://149.165.154.65/data/HDF5EOS/Semeru/miaplpy/overlay.html#/?minScale=-2&amp;maxScale=2</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Lewotolok/miaplpy/overlay.html#/start/-8.2727/123.5110/14.6000?minScale=-1.5&amp;maxScale=1.5&amp;pixelSize=5.5&amp;background=satellite</t>
   </si>
 </sst>
 </file>
@@ -21357,7 +21357,7 @@
     </row>
     <row r="338" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="6" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B338" s="3">
         <v>261080</v>
@@ -21841,7 +21841,7 @@
     </row>
     <row r="349" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="6" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B349" s="3">
         <v>261170</v>
@@ -23337,7 +23337,7 @@
     </row>
     <row r="383" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="6" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B383" s="3">
         <v>263250</v>
@@ -23425,7 +23425,7 @@
     </row>
     <row r="385" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="6" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B385" s="3">
         <v>263300</v>
@@ -23821,7 +23821,7 @@
     </row>
     <row r="394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="6" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B394" s="3">
         <v>264020</v>
@@ -23865,7 +23865,7 @@
     </row>
     <row r="395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="6" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B395" s="3">
         <v>264030</v>
@@ -23909,7 +23909,7 @@
     </row>
     <row r="396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="6" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B396" s="3">
         <v>264040</v>
@@ -23997,7 +23997,7 @@
     </row>
     <row r="398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="6" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B398" s="3">
         <v>264180</v>
@@ -24129,7 +24129,7 @@
     </row>
     <row r="401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="6" t="s">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="B401" s="3">
         <v>264230</v>
@@ -26593,7 +26593,7 @@
     </row>
     <row r="457" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="6" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B457" s="3">
         <v>273010</v>
@@ -26681,7 +26681,7 @@
     </row>
     <row r="459" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B459" s="3">
         <v>273030</v>
@@ -66047,7 +66047,7 @@
     <hyperlink ref="A905" r:id="rId1343" xr:uid="{6F69D3AA-AEA7-1142-9894-0755A8D901C0}"/>
     <hyperlink ref="B905" r:id="rId1344" display="https://volcano.si.edu/volcano.cfm?vn=332010" xr:uid="{49AFC9C8-A551-3948-9FE3-436253A7BFE1}"/>
     <hyperlink ref="A904" r:id="rId1345" display="https://insarmaps.miami.edu/start/19.4032/-155.2273/10.9779?flyToDatasetCenter=false&amp;startDataset=S1_vert_087_124_mintpy_20180902_XXXXXXXX_N1978W15586_N1978W15473_N1912W15473_N1912W15586&amp;pointLat=19.39940&amp;pointLon=-155.27805&amp;minScale=-20&amp;maxScale=20&amp;startDate=20180902&amp;endDate=20260228&amp;pixelSize=3.3" xr:uid="{06950C1A-A714-B24B-BABA-AC6C3B02267A}"/>
-    <hyperlink ref="A401" r:id="rId1346" display="http://149.165.154.65/data/HDF5EOS/Lewotolok/miaiply" xr:uid="{73831688-CC6A-3643-8C99-1F23A35EC407}"/>
+    <hyperlink ref="A401" r:id="rId1346" location="/start/-8.2727/123.5110/14.6000?minScale=-1.5&amp;maxScale=1.5&amp;pixelSize=5.5&amp;background=satellite" xr:uid="{73831688-CC6A-3643-8C99-1F23A35EC407}"/>
     <hyperlink ref="A398" r:id="rId1347" location="/start/-8.5402/122.7753/13.5@minScale=-1.5&amp;maxScale=1.5" xr:uid="{BA612BF8-6BAA-CB4E-9663-BCA3638E8A15}"/>
     <hyperlink ref="A349" r:id="rId1348" location="/start/-1.696/101.270/14.4?minScale=-0.8&amp;maxScale=0.8&amp;background=satellite" xr:uid="{38CAB67B-7C95-0943-9B63-ECFFB44BCC04}"/>
     <hyperlink ref="A396" r:id="rId1349" display="http://149.165.153.50/start/-8.2450/117.9958/12.5292?flyToDatasetCenter=false&amp;startDataset=S1_asc_083_miaplpy_20141023_20250215_S0836E11794_S0832E11809_S0817E11806_S0820E11792_filtDel4DS&amp;minScale=-3&amp;maxScale=3&amp;startDate=20141023&amp;endDate=20250215&amp;pixelSize=2.1&amp;background=satellite" xr:uid="{074096C7-BC89-3546-B9E6-FF4457770D48}"/>

--- a/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/tools/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEB435F-95A0-F841-9DAF-3A76E8D65916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199CC11D-BF77-DC4D-9CD2-977E40459C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3920" yWindow="1900" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
+    <workbookView xWindow="940" yWindow="1900" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11935" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11937" uniqueCount="2015">
   <si>
     <t>Global Volcanism Program - Volcanoes of the World 5.1.0</t>
   </si>
@@ -5933,9 +5933,6 @@
     <t>http://149.165.154.65/data/HDF5EOS/Stromboli/miaplpy</t>
   </si>
   <si>
-    <t>http://149.165.154.65/data/HDF5EOS/Etna/miaplpy</t>
-  </si>
-  <si>
     <t>http://149.165.154.65/data/HDF5EOS/Etna/mintpy</t>
   </si>
   <si>
@@ -6075,6 +6072,15 @@
   </si>
   <si>
     <t>http://149.165.154.65/data/HDF5EOS/Lewotolok/miaplpy/overlay.html#/start/-8.2727/123.5110/14.6000?minScale=-1.5&amp;maxScale=1.5&amp;pixelSize=5.5&amp;background=satellite</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/Pacaya/miaplpy/overlay.html#/?minScale=-5&amp;maxScale=5&amp;background=hillshade&amp;contour=true</t>
+  </si>
+  <si>
+    <t>http://149.165.154.65/data/HDF5EOS/StVincent/miaplpy/overlay.html#/?minScale=-3&amp;maxScale=3</t>
+  </si>
+  <si>
+    <t>FALSE http://149.165.154.65/data/HDF5EOS/Etna/miaplpy</t>
   </si>
 </sst>
 </file>
@@ -6615,7 +6621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="16" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="b">
         <v>0</v>
       </c>
@@ -6659,7 +6665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="b">
         <v>0</v>
       </c>
@@ -6703,7 +6709,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="b">
         <v>0</v>
       </c>
@@ -6747,7 +6753,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="b">
         <v>0</v>
       </c>
@@ -6791,7 +6797,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="b">
         <v>0</v>
       </c>
@@ -6835,7 +6841,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="b">
         <v>0</v>
       </c>
@@ -6879,7 +6885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="b">
         <v>0</v>
       </c>
@@ -6923,7 +6929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="b">
         <v>0</v>
       </c>
@@ -6967,7 +6973,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="b">
         <v>0</v>
       </c>
@@ -7011,7 +7017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>1964</v>
       </c>
@@ -7189,7 +7195,7 @@
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B16" s="3">
         <v>211060</v>
@@ -7233,7 +7239,7 @@
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>1965</v>
+        <v>2014</v>
       </c>
       <c r="B17" s="3">
         <v>211060</v>
@@ -7260,10 +7266,10 @@
         <v>39</v>
       </c>
       <c r="J17" s="1">
-        <v>37.747999999999998</v>
+        <v>37.648000000000003</v>
       </c>
       <c r="K17" s="1">
-        <v>14.999000000000001</v>
+        <v>15.099</v>
       </c>
       <c r="L17" s="1">
         <v>3357</v>
@@ -7319,7 +7325,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="b">
         <v>0</v>
       </c>
@@ -7363,7 +7369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="b">
         <v>0</v>
       </c>
@@ -7407,7 +7413,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="b">
         <v>0</v>
       </c>
@@ -7451,7 +7457,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="b">
         <v>0</v>
       </c>
@@ -7497,7 +7503,7 @@
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B23" s="3">
         <v>212040</v>
@@ -7585,22 +7591,22 @@
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B25" s="3">
         <v>212050</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>88</v>
@@ -7629,22 +7635,22 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B26" s="3">
         <v>212050</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>88</v>
@@ -7673,22 +7679,22 @@
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B27" s="3">
         <v>212050</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>88</v>
@@ -7717,22 +7723,22 @@
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B28" s="3">
         <v>212050</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>88</v>
@@ -7761,22 +7767,22 @@
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B29" s="3">
         <v>212050</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>88</v>
@@ -7841,7 +7847,7 @@
         <v>999</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>42</v>
@@ -21357,7 +21363,7 @@
     </row>
     <row r="338" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B338" s="3">
         <v>261080</v>
@@ -21841,7 +21847,7 @@
     </row>
     <row r="349" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="6" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B349" s="3">
         <v>261170</v>
@@ -23337,7 +23343,7 @@
     </row>
     <row r="383" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="6" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B383" s="3">
         <v>263250</v>
@@ -23425,7 +23431,7 @@
     </row>
     <row r="385" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="6" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B385" s="3">
         <v>263300</v>
@@ -23821,7 +23827,7 @@
     </row>
     <row r="394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="6" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B394" s="3">
         <v>264020</v>
@@ -23865,7 +23871,7 @@
     </row>
     <row r="395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="6" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B395" s="3">
         <v>264030</v>
@@ -23909,7 +23915,7 @@
     </row>
     <row r="396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="6" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B396" s="3">
         <v>264040</v>
@@ -23997,7 +24003,7 @@
     </row>
     <row r="398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="6" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B398" s="3">
         <v>264180</v>
@@ -24129,7 +24135,7 @@
     </row>
     <row r="401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="6" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B401" s="3">
         <v>264230</v>
@@ -26593,7 +26599,7 @@
     </row>
     <row r="457" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="6" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B457" s="3">
         <v>273010</v>
@@ -26681,7 +26687,7 @@
     </row>
     <row r="459" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="6" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B459" s="3">
         <v>273030</v>
@@ -27031,7 +27037,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="467" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="b">
         <v>0</v>
       </c>
@@ -27075,7 +27081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="468" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="b">
         <v>0</v>
       </c>
@@ -27119,7 +27125,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="469" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="b">
         <v>0</v>
       </c>
@@ -27163,7 +27169,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="470" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="b">
         <v>0</v>
       </c>
@@ -27207,7 +27213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="471" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="b">
         <v>0</v>
       </c>
@@ -27251,7 +27257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="472" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="b">
         <v>0</v>
       </c>
@@ -27295,7 +27301,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="473" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="b">
         <v>0</v>
       </c>
@@ -27339,7 +27345,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="474" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="b">
         <v>0</v>
       </c>
@@ -27383,7 +27389,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="475" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="b">
         <v>0</v>
       </c>
@@ -27427,7 +27433,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="476" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="b">
         <v>0</v>
       </c>
@@ -27471,7 +27477,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="477" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="b">
         <v>0</v>
       </c>
@@ -27515,7 +27521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="478" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="b">
         <v>0</v>
       </c>
@@ -27559,7 +27565,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="479" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="b">
         <v>0</v>
       </c>
@@ -27603,7 +27609,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="480" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="b">
         <v>0</v>
       </c>
@@ -27647,7 +27653,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="481" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="b">
         <v>0</v>
       </c>
@@ -27691,7 +27697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="482" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="b">
         <v>0</v>
       </c>
@@ -27735,7 +27741,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="483" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="b">
         <v>0</v>
       </c>
@@ -27779,7 +27785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="484" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="b">
         <v>0</v>
       </c>
@@ -27823,7 +27829,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="485" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="b">
         <v>0</v>
       </c>
@@ -27867,7 +27873,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="486" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="b">
         <v>0</v>
       </c>
@@ -27911,7 +27917,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="487" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="b">
         <v>0</v>
       </c>
@@ -27955,7 +27961,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="488" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="b">
         <v>0</v>
       </c>
@@ -27999,7 +28005,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="489" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="b">
         <v>0</v>
       </c>
@@ -28043,7 +28049,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="490" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="b">
         <v>0</v>
       </c>
@@ -28087,7 +28093,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="491" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="b">
         <v>0</v>
       </c>
@@ -28131,7 +28137,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="492" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="b">
         <v>0</v>
       </c>
@@ -28175,7 +28181,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="493" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="b">
         <v>0</v>
       </c>
@@ -28219,7 +28225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="494" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="b">
         <v>0</v>
       </c>
@@ -28263,7 +28269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="495" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="b">
         <v>0</v>
       </c>
@@ -28307,7 +28313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="496" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="b">
         <v>0</v>
       </c>
@@ -28351,7 +28357,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="497" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="b">
         <v>0</v>
       </c>
@@ -28395,7 +28401,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="498" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="b">
         <v>0</v>
       </c>
@@ -28439,7 +28445,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="499" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="b">
         <v>0</v>
       </c>
@@ -28483,7 +28489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="500" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="b">
         <v>0</v>
       </c>
@@ -28527,7 +28533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="501" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="b">
         <v>0</v>
       </c>
@@ -28571,7 +28577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="502" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="b">
         <v>0</v>
       </c>
@@ -28615,7 +28621,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="503" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="b">
         <v>0</v>
       </c>
@@ -28659,7 +28665,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="504" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="b">
         <v>0</v>
       </c>
@@ -28703,7 +28709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="505" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="b">
         <v>0</v>
       </c>
@@ -28747,7 +28753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="506" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="b">
         <v>0</v>
       </c>
@@ -28791,7 +28797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="507" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="b">
         <v>0</v>
       </c>
@@ -28835,7 +28841,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="508" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="b">
         <v>0</v>
       </c>
@@ -28879,7 +28885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="509" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="b">
         <v>0</v>
       </c>
@@ -28923,7 +28929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="510" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="b">
         <v>0</v>
       </c>
@@ -28967,7 +28973,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="511" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="b">
         <v>0</v>
       </c>
@@ -29011,7 +29017,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="512" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="b">
         <v>0</v>
       </c>
@@ -29055,7 +29061,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="513" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="b">
         <v>0</v>
       </c>
@@ -29099,7 +29105,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="514" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="b">
         <v>0</v>
       </c>
@@ -29143,7 +29149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="515" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="b">
         <v>0</v>
       </c>
@@ -29187,7 +29193,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="516" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="b">
         <v>0</v>
       </c>
@@ -29231,7 +29237,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="517" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="b">
         <v>0</v>
       </c>
@@ -29275,7 +29281,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="518" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="b">
         <v>0</v>
       </c>
@@ -29319,7 +29325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="519" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="b">
         <v>0</v>
       </c>
@@ -29363,7 +29369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="520" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="b">
         <v>0</v>
       </c>
@@ -29407,7 +29413,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="521" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="b">
         <v>0</v>
       </c>
@@ -29451,7 +29457,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="522" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="b">
         <v>0</v>
       </c>
@@ -29495,7 +29501,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="523" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="b">
         <v>0</v>
       </c>
@@ -29539,7 +29545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="524" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="b">
         <v>0</v>
       </c>
@@ -29583,7 +29589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="525" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="b">
         <v>0</v>
       </c>
@@ -29627,7 +29633,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="526" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="b">
         <v>0</v>
       </c>
@@ -29671,7 +29677,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="527" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="b">
         <v>0</v>
       </c>
@@ -29715,7 +29721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="528" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="1" t="b">
         <v>0</v>
       </c>
@@ -29759,7 +29765,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="529" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="b">
         <v>0</v>
       </c>
@@ -29803,7 +29809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="530" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="b">
         <v>0</v>
       </c>
@@ -29847,7 +29853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="531" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="b">
         <v>0</v>
       </c>
@@ -29891,7 +29897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="532" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="b">
         <v>0</v>
       </c>
@@ -29935,7 +29941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="533" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="b">
         <v>0</v>
       </c>
@@ -29979,7 +29985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="534" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="b">
         <v>0</v>
       </c>
@@ -30023,7 +30029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="535" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="b">
         <v>0</v>
       </c>
@@ -30067,7 +30073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="536" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="b">
         <v>0</v>
       </c>
@@ -30111,7 +30117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="537" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="b">
         <v>0</v>
       </c>
@@ -30155,7 +30161,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="538" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="b">
         <v>0</v>
       </c>
@@ -30199,7 +30205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="539" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="b">
         <v>0</v>
       </c>
@@ -30243,7 +30249,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="540" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="1" t="b">
         <v>0</v>
       </c>
@@ -30287,7 +30293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="541" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="1" t="b">
         <v>0</v>
       </c>
@@ -30331,7 +30337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="542" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="1" t="b">
         <v>0</v>
       </c>
@@ -30375,7 +30381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="543" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="1" t="b">
         <v>0</v>
       </c>
@@ -30419,7 +30425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="544" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="1" t="b">
         <v>0</v>
       </c>
@@ -30463,7 +30469,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="545" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="1" t="b">
         <v>0</v>
       </c>
@@ -30507,7 +30513,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="546" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="1" t="b">
         <v>0</v>
       </c>
@@ -30551,7 +30557,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="547" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="1" t="b">
         <v>0</v>
       </c>
@@ -30595,7 +30601,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="548" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="1" t="b">
         <v>0</v>
       </c>
@@ -30639,7 +30645,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="549" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="b">
         <v>0</v>
       </c>
@@ -30683,7 +30689,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="550" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="b">
         <v>0</v>
       </c>
@@ -30727,7 +30733,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="551" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="1" t="b">
         <v>0</v>
       </c>
@@ -30771,7 +30777,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="552" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="1" t="b">
         <v>0</v>
       </c>
@@ -30815,7 +30821,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="553" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="1" t="b">
         <v>0</v>
       </c>
@@ -30859,7 +30865,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="554" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="1" t="b">
         <v>0</v>
       </c>
@@ -30903,7 +30909,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="555" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="1" t="b">
         <v>0</v>
       </c>
@@ -30947,7 +30953,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="556" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="1" t="b">
         <v>0</v>
       </c>
@@ -30991,7 +30997,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="557" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="1" t="b">
         <v>0</v>
       </c>
@@ -31035,7 +31041,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="558" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="1" t="b">
         <v>0</v>
       </c>
@@ -31079,7 +31085,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="559" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="1" t="b">
         <v>0</v>
       </c>
@@ -31123,7 +31129,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="560" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="1" t="b">
         <v>0</v>
       </c>
@@ -31167,7 +31173,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="561" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="1" t="b">
         <v>0</v>
       </c>
@@ -31211,7 +31217,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="562" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="1" t="b">
         <v>0</v>
       </c>
@@ -31255,7 +31261,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="563" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="1" t="b">
         <v>0</v>
       </c>
@@ -31299,7 +31305,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="564" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="1" t="b">
         <v>0</v>
       </c>
@@ -31343,7 +31349,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="565" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="1" t="b">
         <v>0</v>
       </c>
@@ -31387,7 +31393,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="566" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="1" t="b">
         <v>0</v>
       </c>
@@ -31431,7 +31437,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="567" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="1" t="b">
         <v>0</v>
       </c>
@@ -31475,7 +31481,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="568" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="1" t="b">
         <v>0</v>
       </c>
@@ -31519,7 +31525,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="569" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="1" t="b">
         <v>0</v>
       </c>
@@ -31563,7 +31569,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="570" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="1" t="b">
         <v>0</v>
       </c>
@@ -31607,7 +31613,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="571" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="1" t="b">
         <v>0</v>
       </c>
@@ -31651,7 +31657,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="572" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="1" t="b">
         <v>0</v>
       </c>
@@ -31695,7 +31701,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="573" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="1" t="b">
         <v>0</v>
       </c>
@@ -31739,7 +31745,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="574" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="1" t="b">
         <v>0</v>
       </c>
@@ -31783,7 +31789,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="575" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="1" t="b">
         <v>0</v>
       </c>
@@ -31827,7 +31833,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="576" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="1" t="b">
         <v>0</v>
       </c>
@@ -31871,7 +31877,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="577" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="1" t="b">
         <v>0</v>
       </c>
@@ -31915,7 +31921,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="578" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="1" t="b">
         <v>0</v>
       </c>
@@ -31959,7 +31965,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="579" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="1" t="b">
         <v>0</v>
       </c>
@@ -32003,7 +32009,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="580" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="1" t="b">
         <v>0</v>
       </c>
@@ -32091,7 +32097,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="582" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="1" t="b">
         <v>0</v>
       </c>
@@ -32135,7 +32141,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="583" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="1" t="b">
         <v>0</v>
       </c>
@@ -32179,7 +32185,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="584" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="1" t="b">
         <v>0</v>
       </c>
@@ -32223,7 +32229,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="585" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="1" t="b">
         <v>0</v>
       </c>
@@ -32267,7 +32273,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="586" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="1" t="b">
         <v>0</v>
       </c>
@@ -32311,7 +32317,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="587" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="1" t="b">
         <v>0</v>
       </c>
@@ -32355,7 +32361,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="588" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="1" t="b">
         <v>0</v>
       </c>
@@ -32487,7 +32493,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="591" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="1" t="b">
         <v>0</v>
       </c>
@@ -32531,7 +32537,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="592" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="1" t="b">
         <v>0</v>
       </c>
@@ -32575,7 +32581,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="593" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="1" t="b">
         <v>0</v>
       </c>
@@ -32619,7 +32625,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="594" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="1" t="b">
         <v>0</v>
       </c>
@@ -32663,7 +32669,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="595" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="1" t="b">
         <v>0</v>
       </c>
@@ -32707,7 +32713,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="596" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="1" t="b">
         <v>0</v>
       </c>
@@ -32751,7 +32757,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="597" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="1" t="b">
         <v>0</v>
       </c>
@@ -32795,7 +32801,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="598" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="1" t="b">
         <v>0</v>
       </c>
@@ -32839,7 +32845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="599" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="1" t="b">
         <v>0</v>
       </c>
@@ -32883,7 +32889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="600" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="1" t="b">
         <v>0</v>
       </c>
@@ -32927,7 +32933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="601" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="1" t="b">
         <v>0</v>
       </c>
@@ -32971,7 +32977,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="602" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="1" t="b">
         <v>0</v>
       </c>
@@ -33015,7 +33021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="603" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="1" t="b">
         <v>0</v>
       </c>
@@ -33059,7 +33065,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="604" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="1" t="b">
         <v>0</v>
       </c>
@@ -33103,7 +33109,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="605" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="1" t="b">
         <v>0</v>
       </c>
@@ -33147,7 +33153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="606" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="1" t="b">
         <v>0</v>
       </c>
@@ -33191,7 +33197,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="607" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="1" t="b">
         <v>0</v>
       </c>
@@ -33235,7 +33241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="608" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="1" t="b">
         <v>0</v>
       </c>
@@ -33279,7 +33285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="609" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="1" t="b">
         <v>0</v>
       </c>
@@ -33323,7 +33329,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="610" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="1" t="b">
         <v>0</v>
       </c>
@@ -33367,7 +33373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="611" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="1" t="b">
         <v>0</v>
       </c>
@@ -33411,7 +33417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="612" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="1" t="b">
         <v>0</v>
       </c>
@@ -33455,7 +33461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="613" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="1" t="b">
         <v>0</v>
       </c>
@@ -33499,7 +33505,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="614" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="1" t="b">
         <v>0</v>
       </c>
@@ -33543,7 +33549,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="615" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="1" t="b">
         <v>0</v>
       </c>
@@ -33587,7 +33593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="616" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="1" t="b">
         <v>0</v>
       </c>
@@ -33631,7 +33637,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="617" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="1" t="b">
         <v>0</v>
       </c>
@@ -33675,7 +33681,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="618" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="1" t="b">
         <v>0</v>
       </c>
@@ -33719,7 +33725,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="619" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="1" t="b">
         <v>0</v>
       </c>
@@ -33763,7 +33769,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="620" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="1" t="b">
         <v>0</v>
       </c>
@@ -33807,7 +33813,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="621" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="1" t="b">
         <v>0</v>
       </c>
@@ -33851,7 +33857,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="622" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="1" t="b">
         <v>0</v>
       </c>
@@ -33895,7 +33901,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="623" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="1" t="b">
         <v>0</v>
       </c>
@@ -33939,7 +33945,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="624" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="1" t="b">
         <v>0</v>
       </c>
@@ -33983,7 +33989,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="625" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="1" t="b">
         <v>0</v>
       </c>
@@ -34027,7 +34033,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="626" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="1" t="b">
         <v>0</v>
       </c>
@@ -34071,7 +34077,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="627" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="1" t="b">
         <v>0</v>
       </c>
@@ -34115,7 +34121,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="628" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="1" t="b">
         <v>0</v>
       </c>
@@ -34159,7 +34165,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="629" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="1" t="b">
         <v>0</v>
       </c>
@@ -34203,7 +34209,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="630" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="1" t="b">
         <v>0</v>
       </c>
@@ -34291,7 +34297,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="632" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="1" t="b">
         <v>0</v>
       </c>
@@ -34335,7 +34341,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="633" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="1" t="b">
         <v>0</v>
       </c>
@@ -34379,7 +34385,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="634" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="1" t="b">
         <v>0</v>
       </c>
@@ -34423,7 +34429,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="635" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="1" t="b">
         <v>0</v>
       </c>
@@ -34467,7 +34473,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="636" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="1" t="b">
         <v>0</v>
       </c>
@@ -34511,7 +34517,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="637" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="1" t="b">
         <v>0</v>
       </c>
@@ -34555,7 +34561,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="638" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="1" t="b">
         <v>0</v>
       </c>
@@ -34599,7 +34605,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="639" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="1" t="b">
         <v>0</v>
       </c>
@@ -34643,7 +34649,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="640" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="1" t="b">
         <v>0</v>
       </c>
@@ -34687,7 +34693,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="641" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="1" t="b">
         <v>0</v>
       </c>
@@ -34731,7 +34737,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="642" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="1" t="b">
         <v>0</v>
       </c>
@@ -34775,7 +34781,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="643" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="1" t="b">
         <v>0</v>
       </c>
@@ -34819,7 +34825,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="644" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="1" t="b">
         <v>0</v>
       </c>
@@ -34863,7 +34869,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="645" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="1" t="b">
         <v>0</v>
       </c>
@@ -34907,7 +34913,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="646" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="1" t="b">
         <v>0</v>
       </c>
@@ -34951,7 +34957,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="647" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="1" t="b">
         <v>0</v>
       </c>
@@ -34995,7 +35001,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="648" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="1" t="b">
         <v>0</v>
       </c>
@@ -35039,7 +35045,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="649" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="1" t="b">
         <v>0</v>
       </c>
@@ -35083,7 +35089,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="650" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="1" t="b">
         <v>0</v>
       </c>
@@ -35127,7 +35133,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="651" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="1" t="b">
         <v>0</v>
       </c>
@@ -35171,7 +35177,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="652" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="1" t="b">
         <v>0</v>
       </c>
@@ -35215,7 +35221,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="653" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="1" t="b">
         <v>0</v>
       </c>
@@ -35259,7 +35265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="654" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="1" t="b">
         <v>0</v>
       </c>
@@ -35303,7 +35309,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="655" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="1" t="b">
         <v>0</v>
       </c>
@@ -35347,7 +35353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="656" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="1" t="b">
         <v>0</v>
       </c>
@@ -35391,7 +35397,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="657" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="1" t="b">
         <v>0</v>
       </c>
@@ -35435,7 +35441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="658" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="1" t="b">
         <v>0</v>
       </c>
@@ -35479,7 +35485,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="659" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="1" t="b">
         <v>0</v>
       </c>
@@ -35523,7 +35529,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="660" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="1" t="b">
         <v>0</v>
       </c>
@@ -35567,7 +35573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="661" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="1" t="b">
         <v>0</v>
       </c>
@@ -35611,7 +35617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="662" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="1" t="b">
         <v>0</v>
       </c>
@@ -35655,7 +35661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="663" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="1" t="b">
         <v>0</v>
       </c>
@@ -35699,7 +35705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="664" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="1" t="b">
         <v>0</v>
       </c>
@@ -35743,7 +35749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="665" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="1" t="b">
         <v>0</v>
       </c>
@@ -35787,7 +35793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="666" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="1" t="b">
         <v>0</v>
       </c>
@@ -35831,7 +35837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="667" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="1" t="b">
         <v>0</v>
       </c>
@@ -35875,7 +35881,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="668" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="1" t="b">
         <v>0</v>
       </c>
@@ -35919,7 +35925,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="669" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="1" t="b">
         <v>0</v>
       </c>
@@ -35963,7 +35969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="670" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="1" t="b">
         <v>0</v>
       </c>
@@ -36007,7 +36013,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="671" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="1" t="b">
         <v>0</v>
       </c>
@@ -36051,7 +36057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="672" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="1" t="b">
         <v>0</v>
       </c>
@@ -36095,7 +36101,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="673" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="1" t="b">
         <v>0</v>
       </c>
@@ -36139,7 +36145,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="674" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="1" t="b">
         <v>0</v>
       </c>
@@ -36183,7 +36189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="675" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="1" t="b">
         <v>0</v>
       </c>
@@ -36227,7 +36233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="676" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="1" t="b">
         <v>0</v>
       </c>
@@ -36271,7 +36277,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="677" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="1" t="b">
         <v>0</v>
       </c>
@@ -36315,7 +36321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="678" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="1" t="b">
         <v>0</v>
       </c>
@@ -36359,7 +36365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="679" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="1" t="b">
         <v>0</v>
       </c>
@@ -36403,7 +36409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="680" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="1" t="b">
         <v>0</v>
       </c>
@@ -36447,7 +36453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="681" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="1" t="b">
         <v>0</v>
       </c>
@@ -36491,7 +36497,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="682" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="1" t="b">
         <v>0</v>
       </c>
@@ -36535,7 +36541,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="683" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="1" t="b">
         <v>0</v>
       </c>
@@ -36579,7 +36585,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="684" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="1" t="b">
         <v>0</v>
       </c>
@@ -36623,7 +36629,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="685" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="1" t="b">
         <v>0</v>
       </c>
@@ -36667,7 +36673,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="686" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="1" t="b">
         <v>0</v>
       </c>
@@ -36711,7 +36717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="687" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="1" t="b">
         <v>0</v>
       </c>
@@ -36755,7 +36761,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="688" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="1" t="b">
         <v>0</v>
       </c>
@@ -36799,7 +36805,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="689" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="1" t="b">
         <v>0</v>
       </c>
@@ -36843,7 +36849,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="690" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="1" t="b">
         <v>0</v>
       </c>
@@ -36887,7 +36893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="691" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="1" t="b">
         <v>0</v>
       </c>
@@ -36931,7 +36937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="692" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="1" t="b">
         <v>0</v>
       </c>
@@ -36975,7 +36981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="693" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="1" t="b">
         <v>0</v>
       </c>
@@ -37019,7 +37025,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="694" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="1" t="b">
         <v>0</v>
       </c>
@@ -37063,7 +37069,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="695" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="1" t="b">
         <v>0</v>
       </c>
@@ -37107,7 +37113,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="696" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="1" t="b">
         <v>0</v>
       </c>
@@ -37151,7 +37157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="697" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="1" t="b">
         <v>0</v>
       </c>
@@ -37195,7 +37201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="698" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="1" t="b">
         <v>0</v>
       </c>
@@ -37239,7 +37245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="699" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="1" t="b">
         <v>0</v>
       </c>
@@ -37283,7 +37289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="700" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="1" t="b">
         <v>0</v>
       </c>
@@ -37327,7 +37333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="701" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="1" t="b">
         <v>0</v>
       </c>
@@ -37371,7 +37377,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="702" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="1" t="b">
         <v>0</v>
       </c>
@@ -37415,7 +37421,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="703" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="1" t="b">
         <v>0</v>
       </c>
@@ -37459,7 +37465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="704" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="1" t="b">
         <v>0</v>
       </c>
@@ -37503,7 +37509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="705" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="1" t="b">
         <v>0</v>
       </c>
@@ -37547,7 +37553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="706" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="1" t="b">
         <v>0</v>
       </c>
@@ -37591,7 +37597,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="707" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="1" t="b">
         <v>0</v>
       </c>
@@ -37635,7 +37641,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="708" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="1" t="b">
         <v>0</v>
       </c>
@@ -37679,7 +37685,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="709" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="1" t="b">
         <v>0</v>
       </c>
@@ -37723,7 +37729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="710" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="1" t="b">
         <v>0</v>
       </c>
@@ -37767,7 +37773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="711" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="1" t="b">
         <v>0</v>
       </c>
@@ -37811,7 +37817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="712" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="1" t="b">
         <v>0</v>
       </c>
@@ -37855,7 +37861,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="713" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="1" t="b">
         <v>0</v>
       </c>
@@ -37899,7 +37905,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="714" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="1" t="b">
         <v>0</v>
       </c>
@@ -37943,7 +37949,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="715" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="1" t="b">
         <v>0</v>
       </c>
@@ -37987,7 +37993,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="716" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="1" t="b">
         <v>0</v>
       </c>
@@ -38031,7 +38037,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="717" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="1" t="b">
         <v>0</v>
       </c>
@@ -38075,7 +38081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="718" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="1" t="b">
         <v>0</v>
       </c>
@@ -38119,7 +38125,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="719" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="1" t="b">
         <v>0</v>
       </c>
@@ -38163,7 +38169,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="720" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="1" t="b">
         <v>0</v>
       </c>
@@ -38207,7 +38213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="721" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="1" t="b">
         <v>0</v>
       </c>
@@ -38251,7 +38257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="722" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="1" t="b">
         <v>0</v>
       </c>
@@ -38295,7 +38301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="723" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="1" t="b">
         <v>0</v>
       </c>
@@ -38339,7 +38345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="724" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="1" t="b">
         <v>0</v>
       </c>
@@ -38383,7 +38389,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="725" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="1" t="b">
         <v>0</v>
       </c>
@@ -38427,7 +38433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="726" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="1" t="b">
         <v>0</v>
       </c>
@@ -38471,7 +38477,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="727" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="1" t="b">
         <v>0</v>
       </c>
@@ -38515,7 +38521,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="728" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="1" t="b">
         <v>0</v>
       </c>
@@ -38559,7 +38565,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="729" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="1" t="b">
         <v>0</v>
       </c>
@@ -38603,7 +38609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="730" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="1" t="b">
         <v>0</v>
       </c>
@@ -38647,7 +38653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="731" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="1" t="b">
         <v>0</v>
       </c>
@@ -38691,7 +38697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="732" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="1" t="b">
         <v>0</v>
       </c>
@@ -38735,7 +38741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="733" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="1" t="b">
         <v>0</v>
       </c>
@@ -38779,7 +38785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="734" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="1" t="b">
         <v>0</v>
       </c>
@@ -38823,7 +38829,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="735" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="1" t="b">
         <v>0</v>
       </c>
@@ -38867,7 +38873,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="736" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="1" t="b">
         <v>0</v>
       </c>
@@ -38911,7 +38917,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="737" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="1" t="b">
         <v>0</v>
       </c>
@@ -38955,7 +38961,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="738" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="1" t="b">
         <v>0</v>
       </c>
@@ -38999,7 +39005,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="739" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="1" t="b">
         <v>0</v>
       </c>
@@ -39043,7 +39049,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="740" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="1" t="b">
         <v>0</v>
       </c>
@@ -39087,7 +39093,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="741" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="1" t="b">
         <v>0</v>
       </c>
@@ -39175,7 +39181,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="743" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="1" t="b">
         <v>0</v>
       </c>
@@ -39219,7 +39225,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="744" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="1" t="b">
         <v>0</v>
       </c>
@@ -39263,7 +39269,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="745" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="1" t="b">
         <v>0</v>
       </c>
@@ -39307,7 +39313,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="746" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="1" t="b">
         <v>0</v>
       </c>
@@ -39395,7 +39401,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="748" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="1" t="b">
         <v>0</v>
       </c>
@@ -39439,7 +39445,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="749" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="1" t="b">
         <v>0</v>
       </c>
@@ -39483,7 +39489,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="750" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="1" t="b">
         <v>0</v>
       </c>
@@ -39527,7 +39533,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="751" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="1" t="b">
         <v>0</v>
       </c>
@@ -39571,7 +39577,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="752" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="1" t="b">
         <v>0</v>
       </c>
@@ -39615,7 +39621,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="753" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="1" t="b">
         <v>0</v>
       </c>
@@ -39659,7 +39665,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="754" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="1" t="b">
         <v>0</v>
       </c>
@@ -39703,7 +39709,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="755" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="1" t="b">
         <v>0</v>
       </c>
@@ -39747,7 +39753,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="756" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="1" t="b">
         <v>0</v>
       </c>
@@ -39791,7 +39797,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="757" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="1" t="b">
         <v>0</v>
       </c>
@@ -39835,7 +39841,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="758" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="1" t="b">
         <v>0</v>
       </c>
@@ -39879,7 +39885,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="759" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="1" t="b">
         <v>0</v>
       </c>
@@ -39923,7 +39929,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="760" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="1" t="b">
         <v>0</v>
       </c>
@@ -39967,7 +39973,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="761" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="1" t="b">
         <v>0</v>
       </c>
@@ -40011,7 +40017,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="762" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="1" t="b">
         <v>0</v>
       </c>
@@ -40055,7 +40061,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="763" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="1" t="b">
         <v>0</v>
       </c>
@@ -40099,7 +40105,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="764" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="1" t="b">
         <v>0</v>
       </c>
@@ -40143,7 +40149,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="765" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="1" t="b">
         <v>0</v>
       </c>
@@ -40187,7 +40193,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="766" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="1" t="b">
         <v>0</v>
       </c>
@@ -40231,7 +40237,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="767" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="1" t="b">
         <v>0</v>
       </c>
@@ -40275,7 +40281,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="768" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="1" t="b">
         <v>0</v>
       </c>
@@ -40319,7 +40325,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="769" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="1" t="b">
         <v>0</v>
       </c>
@@ -40363,7 +40369,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="770" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="1" t="b">
         <v>0</v>
       </c>
@@ -40407,7 +40413,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="771" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="1" t="b">
         <v>0</v>
       </c>
@@ -40451,7 +40457,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="772" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="1" t="b">
         <v>0</v>
       </c>
@@ -40495,7 +40501,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="773" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="1" t="b">
         <v>0</v>
       </c>
@@ -40539,7 +40545,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="774" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="1" t="b">
         <v>0</v>
       </c>
@@ -40583,7 +40589,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="775" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="1" t="b">
         <v>0</v>
       </c>
@@ -40627,7 +40633,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="776" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="1" t="b">
         <v>0</v>
       </c>
@@ -40671,7 +40677,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="777" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="1" t="b">
         <v>0</v>
       </c>
@@ -40715,7 +40721,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="778" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="1" t="b">
         <v>0</v>
       </c>
@@ -40759,7 +40765,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="779" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="1" t="b">
         <v>0</v>
       </c>
@@ -40803,7 +40809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="780" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="1" t="b">
         <v>0</v>
       </c>
@@ -40847,7 +40853,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="781" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="1" t="b">
         <v>0</v>
       </c>
@@ -40891,7 +40897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="782" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="1" t="b">
         <v>0</v>
       </c>
@@ -40935,7 +40941,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="783" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="1" t="b">
         <v>0</v>
       </c>
@@ -40979,7 +40985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="784" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="1" t="b">
         <v>0</v>
       </c>
@@ -41023,7 +41029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="785" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="1" t="b">
         <v>0</v>
       </c>
@@ -41067,7 +41073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="786" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="1" t="b">
         <v>0</v>
       </c>
@@ -41111,7 +41117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="787" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="1" t="b">
         <v>0</v>
       </c>
@@ -41155,7 +41161,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="788" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="1" t="b">
         <v>0</v>
       </c>
@@ -41199,7 +41205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="789" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="1" t="b">
         <v>0</v>
       </c>
@@ -41243,7 +41249,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="790" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="1" t="b">
         <v>0</v>
       </c>
@@ -41287,7 +41293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="791" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="1" t="b">
         <v>0</v>
       </c>
@@ -41331,7 +41337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="792" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="1" t="b">
         <v>0</v>
       </c>
@@ -41375,7 +41381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="793" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="1" t="b">
         <v>0</v>
       </c>
@@ -41419,7 +41425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="794" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="1" t="b">
         <v>0</v>
       </c>
@@ -41463,7 +41469,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="795" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="1" t="b">
         <v>0</v>
       </c>
@@ -41507,7 +41513,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="796" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="1" t="b">
         <v>0</v>
       </c>
@@ -41551,7 +41557,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="797" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="1" t="b">
         <v>0</v>
       </c>
@@ -41595,7 +41601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="798" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="1" t="b">
         <v>0</v>
       </c>
@@ -41639,7 +41645,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="799" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="1" t="b">
         <v>0</v>
       </c>
@@ -41683,7 +41689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="800" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="1" t="b">
         <v>0</v>
       </c>
@@ -41727,7 +41733,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="801" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="1" t="b">
         <v>0</v>
       </c>
@@ -41771,7 +41777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="802" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="1" t="b">
         <v>0</v>
       </c>
@@ -41815,7 +41821,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="803" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="1" t="b">
         <v>0</v>
       </c>
@@ -41859,7 +41865,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="804" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="1" t="b">
         <v>0</v>
       </c>
@@ -41903,7 +41909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="805" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="1" t="b">
         <v>0</v>
       </c>
@@ -41947,7 +41953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="806" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="1" t="b">
         <v>0</v>
       </c>
@@ -41991,7 +41997,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="807" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="1" t="b">
         <v>0</v>
       </c>
@@ -42035,7 +42041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="808" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="1" t="b">
         <v>0</v>
       </c>
@@ -42079,7 +42085,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="809" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="1" t="b">
         <v>0</v>
       </c>
@@ -42123,7 +42129,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="810" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="1" t="b">
         <v>0</v>
       </c>
@@ -42167,7 +42173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="811" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="1" t="b">
         <v>0</v>
       </c>
@@ -42211,7 +42217,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="812" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="1" t="b">
         <v>0</v>
       </c>
@@ -42255,7 +42261,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="1" t="b">
         <v>0</v>
       </c>
@@ -42299,7 +42305,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="814" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="1" t="b">
         <v>0</v>
       </c>
@@ -42343,7 +42349,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="815" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="1" t="b">
         <v>0</v>
       </c>
@@ -42387,7 +42393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="816" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="1" t="b">
         <v>0</v>
       </c>
@@ -42431,7 +42437,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="817" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="1" t="b">
         <v>0</v>
       </c>
@@ -42475,7 +42481,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="818" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="1" t="b">
         <v>0</v>
       </c>
@@ -42519,7 +42525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="819" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="1" t="b">
         <v>0</v>
       </c>
@@ -42563,7 +42569,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="820" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="1" t="b">
         <v>0</v>
       </c>
@@ -42607,7 +42613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="821" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="1" t="b">
         <v>0</v>
       </c>
@@ -42651,7 +42657,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="822" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="1" t="b">
         <v>0</v>
       </c>
@@ -42695,7 +42701,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="823" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="1" t="b">
         <v>0</v>
       </c>
@@ -42739,7 +42745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="824" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="1" t="b">
         <v>0</v>
       </c>
@@ -42783,7 +42789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="825" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="1" t="b">
         <v>0</v>
       </c>
@@ -42827,7 +42833,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="826" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="1" t="b">
         <v>0</v>
       </c>
@@ -42871,7 +42877,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="827" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="1" t="b">
         <v>0</v>
       </c>
@@ -42915,7 +42921,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="828" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="1" t="b">
         <v>0</v>
       </c>
@@ -42959,7 +42965,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="829" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="1" t="b">
         <v>0</v>
       </c>
@@ -43003,7 +43009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="830" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="1" t="b">
         <v>0</v>
       </c>
@@ -43047,7 +43053,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="831" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="1" t="b">
         <v>0</v>
       </c>
@@ -43091,7 +43097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="832" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="1" t="b">
         <v>0</v>
       </c>
@@ -43135,7 +43141,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="833" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="1" t="b">
         <v>0</v>
       </c>
@@ -43179,7 +43185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="834" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="1" t="b">
         <v>0</v>
       </c>
@@ -43223,7 +43229,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="835" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="1" t="b">
         <v>0</v>
       </c>
@@ -43267,7 +43273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="836" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="1" t="b">
         <v>0</v>
       </c>
@@ -43311,7 +43317,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="837" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="1" t="b">
         <v>0</v>
       </c>
@@ -43355,7 +43361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="838" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="1" t="b">
         <v>0</v>
       </c>
@@ -43399,7 +43405,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="839" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="1" t="b">
         <v>0</v>
       </c>
@@ -43443,7 +43449,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="840" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="1" t="b">
         <v>0</v>
       </c>
@@ -43487,7 +43493,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="841" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="1" t="b">
         <v>0</v>
       </c>
@@ -43531,7 +43537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="842" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="1" t="b">
         <v>0</v>
       </c>
@@ -43575,7 +43581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="843" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="1" t="b">
         <v>0</v>
       </c>
@@ -43619,7 +43625,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="844" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="1" t="b">
         <v>0</v>
       </c>
@@ -43663,7 +43669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="845" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="1" t="b">
         <v>0</v>
       </c>
@@ -43707,7 +43713,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="846" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="1" t="b">
         <v>0</v>
       </c>
@@ -43751,7 +43757,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="847" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="1" t="b">
         <v>0</v>
       </c>
@@ -43795,7 +43801,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="848" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="1" t="b">
         <v>0</v>
       </c>
@@ -43839,7 +43845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="849" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="1" t="b">
         <v>0</v>
       </c>
@@ -43927,7 +43933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="851" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="1" t="b">
         <v>0</v>
       </c>
@@ -43971,7 +43977,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="852" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="1" t="b">
         <v>0</v>
       </c>
@@ -44015,7 +44021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="853" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="1" t="b">
         <v>0</v>
       </c>
@@ -44103,7 +44109,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="855" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="1" t="b">
         <v>0</v>
       </c>
@@ -44147,7 +44153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="856" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="1" t="b">
         <v>0</v>
       </c>
@@ -44191,7 +44197,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="857" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="1" t="b">
         <v>0</v>
       </c>
@@ -44235,7 +44241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="858" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="1" t="b">
         <v>0</v>
       </c>
@@ -44279,7 +44285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="859" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="1" t="b">
         <v>0</v>
       </c>
@@ -44323,7 +44329,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="860" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="1" t="b">
         <v>0</v>
       </c>
@@ -44367,7 +44373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="861" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="1" t="b">
         <v>0</v>
       </c>
@@ -44411,7 +44417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="862" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="1" t="b">
         <v>0</v>
       </c>
@@ -44455,7 +44461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="863" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="1" t="b">
         <v>0</v>
       </c>
@@ -44499,7 +44505,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="864" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="1" t="b">
         <v>0</v>
       </c>
@@ -44543,7 +44549,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="865" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="1" t="b">
         <v>0</v>
       </c>
@@ -44587,7 +44593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="866" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="1" t="b">
         <v>0</v>
       </c>
@@ -44631,7 +44637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="867" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="1" t="b">
         <v>0</v>
       </c>
@@ -44675,7 +44681,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="868" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="1" t="b">
         <v>0</v>
       </c>
@@ -44719,7 +44725,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="869" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="1" t="b">
         <v>0</v>
       </c>
@@ -44763,7 +44769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="870" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="1" t="b">
         <v>0</v>
       </c>
@@ -44807,7 +44813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="871" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="1" t="b">
         <v>0</v>
       </c>
@@ -44939,7 +44945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="874" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="1" t="b">
         <v>0</v>
       </c>
@@ -44983,7 +44989,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="875" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="1" t="b">
         <v>0</v>
       </c>
@@ -45027,7 +45033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="876" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="1" t="b">
         <v>0</v>
       </c>
@@ -45071,7 +45077,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="877" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="1" t="b">
         <v>0</v>
       </c>
@@ -45115,7 +45121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="878" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="1" t="b">
         <v>0</v>
       </c>
@@ -45159,7 +45165,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="879" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="1" t="b">
         <v>0</v>
       </c>
@@ -45203,7 +45209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="880" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="1" t="b">
         <v>0</v>
       </c>
@@ -45247,7 +45253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="881" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="1" t="b">
         <v>0</v>
       </c>
@@ -45291,7 +45297,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="882" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="1" t="b">
         <v>0</v>
       </c>
@@ -45335,7 +45341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="883" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="1" t="b">
         <v>0</v>
       </c>
@@ -45379,7 +45385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="884" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="1" t="b">
         <v>0</v>
       </c>
@@ -45423,7 +45429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="885" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="1" t="b">
         <v>0</v>
       </c>
@@ -45467,7 +45473,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="886" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="1" t="b">
         <v>0</v>
       </c>
@@ -45511,7 +45517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="887" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="1" t="b">
         <v>0</v>
       </c>
@@ -45555,7 +45561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="888" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="1" t="b">
         <v>0</v>
       </c>
@@ -45599,7 +45605,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="889" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="1" t="b">
         <v>0</v>
       </c>
@@ -45643,7 +45649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="890" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="1" t="b">
         <v>0</v>
       </c>
@@ -45687,7 +45693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="891" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="1" t="b">
         <v>0</v>
       </c>
@@ -45731,7 +45737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="892" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="1" t="b">
         <v>0</v>
       </c>
@@ -45775,7 +45781,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="893" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="1" t="b">
         <v>0</v>
       </c>
@@ -45819,7 +45825,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="894" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="1" t="b">
         <v>0</v>
       </c>
@@ -45863,7 +45869,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="895" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="1" t="b">
         <v>0</v>
       </c>
@@ -45907,7 +45913,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="896" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="1" t="b">
         <v>0</v>
       </c>
@@ -45951,7 +45957,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="897" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="1" t="b">
         <v>0</v>
       </c>
@@ -45995,7 +46001,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="898" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="1" t="b">
         <v>0</v>
       </c>
@@ -46039,7 +46045,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="899" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="1" t="b">
         <v>0</v>
       </c>
@@ -46083,7 +46089,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="900" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="1" t="b">
         <v>0</v>
       </c>
@@ -46127,7 +46133,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="901" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="1" t="b">
         <v>0</v>
       </c>
@@ -46171,7 +46177,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="902" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="1" t="b">
         <v>0</v>
       </c>
@@ -46215,7 +46221,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="903" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="1" t="b">
         <v>0</v>
       </c>
@@ -46261,13 +46267,13 @@
     </row>
     <row r="904" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="6" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B904" s="3">
         <v>332010</v>
       </c>
       <c r="C904" s="1" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D904" s="1" t="s">
         <v>446</v>
@@ -46305,13 +46311,13 @@
     </row>
     <row r="905" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="6" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B905" s="3">
         <v>332010</v>
       </c>
       <c r="C905" s="1" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="D905" s="1" t="s">
         <v>446</v>
@@ -46349,19 +46355,19 @@
     </row>
     <row r="906" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="6" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B906" s="3">
         <v>332010</v>
       </c>
       <c r="C906" s="1" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="D906" s="1" t="s">
         <v>446</v>
       </c>
       <c r="E906" s="1" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="F906" s="1" t="s">
         <v>44</v>
@@ -46393,13 +46399,13 @@
     </row>
     <row r="907" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="1" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B907" s="3">
         <v>332020</v>
       </c>
       <c r="C907" s="1" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D907" s="1" t="s">
         <v>446</v>
@@ -46435,7 +46441,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="908" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="1" t="b">
         <v>0</v>
       </c>
@@ -46479,7 +46485,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="909" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A909" s="1" t="b">
         <v>0</v>
       </c>
@@ -46523,7 +46529,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="910" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A910" s="1" t="b">
         <v>0</v>
       </c>
@@ -46567,7 +46573,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="911" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="1" t="b">
         <v>0</v>
       </c>
@@ -46611,7 +46617,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="912" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A912" s="1" t="b">
         <v>0</v>
       </c>
@@ -46655,7 +46661,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="913" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A913" s="1" t="b">
         <v>0</v>
       </c>
@@ -46699,7 +46705,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="914" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A914" s="1" t="b">
         <v>0</v>
       </c>
@@ -46743,7 +46749,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="915" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A915" s="1" t="b">
         <v>0</v>
       </c>
@@ -46787,7 +46793,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="916" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A916" s="1" t="b">
         <v>0</v>
       </c>
@@ -46831,7 +46837,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="917" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A917" s="1" t="b">
         <v>0</v>
       </c>
@@ -46875,7 +46881,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="918" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="1" t="b">
         <v>0</v>
       </c>
@@ -46919,7 +46925,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="919" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A919" s="1" t="b">
         <v>0</v>
       </c>
@@ -46963,7 +46969,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="920" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A920" s="1" t="b">
         <v>0</v>
       </c>
@@ -47007,7 +47013,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="921" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A921" s="1" t="b">
         <v>0</v>
       </c>
@@ -47051,7 +47057,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="922" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A922" s="1" t="b">
         <v>0</v>
       </c>
@@ -47095,7 +47101,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="923" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A923" s="1" t="b">
         <v>0</v>
       </c>
@@ -47139,7 +47145,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="924" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A924" s="1" t="b">
         <v>0</v>
       </c>
@@ -47183,7 +47189,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="925" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A925" s="1" t="b">
         <v>0</v>
       </c>
@@ -47227,7 +47233,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="926" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A926" s="1" t="b">
         <v>0</v>
       </c>
@@ -47271,7 +47277,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="927" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A927" s="1" t="b">
         <v>0</v>
       </c>
@@ -47315,7 +47321,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="928" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A928" s="1" t="b">
         <v>0</v>
       </c>
@@ -47359,7 +47365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="929" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A929" s="1" t="b">
         <v>0</v>
       </c>
@@ -47403,7 +47409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="930" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="1" t="b">
         <v>0</v>
       </c>
@@ -47447,7 +47453,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="931" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A931" s="1" t="b">
         <v>0</v>
       </c>
@@ -47491,7 +47497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="932" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A932" s="1" t="b">
         <v>0</v>
       </c>
@@ -47535,7 +47541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="933" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A933" s="1" t="b">
         <v>0</v>
       </c>
@@ -47579,7 +47585,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="934" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A934" s="1" t="b">
         <v>0</v>
       </c>
@@ -47623,7 +47629,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="935" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A935" s="1" t="b">
         <v>0</v>
       </c>
@@ -47667,7 +47673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="936" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A936" s="1" t="b">
         <v>0</v>
       </c>
@@ -47711,7 +47717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="937" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A937" s="1" t="b">
         <v>0</v>
       </c>
@@ -47755,7 +47761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="938" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A938" s="1" t="b">
         <v>0</v>
       </c>
@@ -47799,7 +47805,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="939" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A939" s="1" t="b">
         <v>0</v>
       </c>
@@ -47843,7 +47849,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="940" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A940" s="1" t="b">
         <v>0</v>
       </c>
@@ -47887,7 +47893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="941" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A941" s="1" t="b">
         <v>0</v>
       </c>
@@ -47931,7 +47937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="942" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A942" s="1" t="b">
         <v>0</v>
       </c>
@@ -47975,7 +47981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="943" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A943" s="1" t="b">
         <v>0</v>
       </c>
@@ -48063,7 +48069,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="945" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A945" s="1" t="b">
         <v>0</v>
       </c>
@@ -48107,7 +48113,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="946" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A946" s="1" t="b">
         <v>0</v>
       </c>
@@ -48151,7 +48157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="947" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A947" s="1" t="b">
         <v>0</v>
       </c>
@@ -48195,7 +48201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="948" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A948" s="1" t="b">
         <v>0</v>
       </c>
@@ -48239,7 +48245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="949" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A949" s="1" t="b">
         <v>0</v>
       </c>
@@ -48283,7 +48289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="950" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A950" s="1" t="b">
         <v>0</v>
       </c>
@@ -48327,7 +48333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="951" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A951" s="1" t="b">
         <v>0</v>
       </c>
@@ -48371,7 +48377,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="952" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A952" s="1" t="b">
         <v>0</v>
       </c>
@@ -48415,7 +48421,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="953" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A953" s="1" t="b">
         <v>0</v>
       </c>
@@ -48459,7 +48465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="954" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A954" s="1" t="b">
         <v>0</v>
       </c>
@@ -48503,7 +48509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="955" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A955" s="1" t="b">
         <v>0</v>
       </c>
@@ -48547,7 +48553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="956" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A956" s="1" t="b">
         <v>0</v>
       </c>
@@ -48591,7 +48597,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="957" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A957" s="1" t="b">
         <v>0</v>
       </c>
@@ -48635,7 +48641,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="958" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A958" s="1" t="b">
         <v>0</v>
       </c>
@@ -48679,7 +48685,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="959" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="1" t="b">
         <v>0</v>
       </c>
@@ -48723,7 +48729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="960" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="1" t="b">
         <v>0</v>
       </c>
@@ -48767,7 +48773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="961" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="1" t="b">
         <v>0</v>
       </c>
@@ -48811,7 +48817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="962" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="1" t="b">
         <v>0</v>
       </c>
@@ -48855,7 +48861,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="963" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="1" t="b">
         <v>0</v>
       </c>
@@ -48899,7 +48905,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="964" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A964" s="1" t="b">
         <v>0</v>
       </c>
@@ -48943,7 +48949,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="965" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A965" s="1" t="b">
         <v>0</v>
       </c>
@@ -48987,7 +48993,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="966" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A966" s="1" t="b">
         <v>0</v>
       </c>
@@ -49031,7 +49037,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="967" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A967" s="1" t="b">
         <v>0</v>
       </c>
@@ -49075,7 +49081,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="968" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="1" t="b">
         <v>0</v>
       </c>
@@ -49207,7 +49213,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="971" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A971" s="1" t="b">
         <v>0</v>
       </c>
@@ -49252,8 +49258,8 @@
       </c>
     </row>
     <row r="972" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A972" s="1" t="b">
-        <v>0</v>
+      <c r="A972" s="6" t="s">
+        <v>2012</v>
       </c>
       <c r="B972" s="3">
         <v>342110</v>
@@ -49295,7 +49301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="973" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A973" s="1" t="b">
         <v>0</v>
       </c>
@@ -49339,7 +49345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="974" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A974" s="1" t="b">
         <v>0</v>
       </c>
@@ -49383,7 +49389,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="975" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A975" s="1" t="b">
         <v>0</v>
       </c>
@@ -49427,7 +49433,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="976" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="1" t="b">
         <v>0</v>
       </c>
@@ -49471,7 +49477,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="977" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A977" s="1" t="b">
         <v>0</v>
       </c>
@@ -49515,7 +49521,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="978" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A978" s="1" t="b">
         <v>0</v>
       </c>
@@ -49559,7 +49565,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="979" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="1" t="b">
         <v>0</v>
       </c>
@@ -49603,7 +49609,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="980" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A980" s="1" t="b">
         <v>0</v>
       </c>
@@ -49647,7 +49653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="981" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A981" s="1" t="b">
         <v>0</v>
       </c>
@@ -49691,7 +49697,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="982" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A982" s="1" t="b">
         <v>0</v>
       </c>
@@ -49735,7 +49741,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="983" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A983" s="1" t="b">
         <v>0</v>
       </c>
@@ -49779,7 +49785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="984" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A984" s="1" t="b">
         <v>0</v>
       </c>
@@ -49823,7 +49829,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="985" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A985" s="1" t="b">
         <v>0</v>
       </c>
@@ -49867,7 +49873,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="986" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A986" s="1" t="b">
         <v>0</v>
       </c>
@@ -49911,7 +49917,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="987" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A987" s="1" t="b">
         <v>0</v>
       </c>
@@ -49955,7 +49961,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="988" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A988" s="1" t="b">
         <v>0</v>
       </c>
@@ -49999,7 +50005,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="989" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A989" s="1" t="b">
         <v>0</v>
       </c>
@@ -50043,7 +50049,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="990" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A990" s="1" t="b">
         <v>0</v>
       </c>
@@ -50087,7 +50093,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="991" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A991" s="1" t="b">
         <v>0</v>
       </c>
@@ -50131,7 +50137,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="992" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A992" s="1" t="b">
         <v>0</v>
       </c>
@@ -50175,7 +50181,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="993" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A993" s="1" t="b">
         <v>0</v>
       </c>
@@ -50219,7 +50225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="994" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A994" s="1" t="b">
         <v>0</v>
       </c>
@@ -50263,7 +50269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="995" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A995" s="1" t="b">
         <v>0</v>
       </c>
@@ -50307,7 +50313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="996" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A996" s="1" t="b">
         <v>0</v>
       </c>
@@ -50351,7 +50357,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="997" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A997" s="1" t="b">
         <v>0</v>
       </c>
@@ -50395,7 +50401,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="998" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A998" s="1" t="b">
         <v>0</v>
       </c>
@@ -50439,7 +50445,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="999" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="1" t="b">
         <v>0</v>
       </c>
@@ -50483,7 +50489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1000" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="1" t="b">
         <v>0</v>
       </c>
@@ -50527,7 +50533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1001" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="1" t="b">
         <v>0</v>
       </c>
@@ -50571,7 +50577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1002" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="1" t="b">
         <v>0</v>
       </c>
@@ -50703,7 +50709,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1005" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="1" t="b">
         <v>0</v>
       </c>
@@ -50747,7 +50753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1006" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="1" t="b">
         <v>0</v>
       </c>
@@ -50791,7 +50797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1007" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="1" t="b">
         <v>0</v>
       </c>
@@ -50879,7 +50885,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1009" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="1" t="b">
         <v>0</v>
       </c>
@@ -50923,7 +50929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1010" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="1" t="b">
         <v>0</v>
       </c>
@@ -51099,7 +51105,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1014" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="1" t="b">
         <v>0</v>
       </c>
@@ -51143,7 +51149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1015" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="1" t="b">
         <v>0</v>
       </c>
@@ -51319,7 +51325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1019" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1019" s="1" t="b">
         <v>0</v>
       </c>
@@ -51363,7 +51369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1020" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1020" s="1" t="b">
         <v>0</v>
       </c>
@@ -51407,7 +51413,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1021" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1021" s="1" t="b">
         <v>0</v>
       </c>
@@ -51451,7 +51457,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1022" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1022" s="1" t="b">
         <v>0</v>
       </c>
@@ -51495,7 +51501,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1023" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1023" s="1" t="b">
         <v>0</v>
       </c>
@@ -51627,7 +51633,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1026" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1026" s="1" t="b">
         <v>0</v>
       </c>
@@ -51671,7 +51677,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1027" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1027" s="1" t="b">
         <v>0</v>
       </c>
@@ -51715,7 +51721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1028" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1028" s="1" t="b">
         <v>0</v>
       </c>
@@ -51759,7 +51765,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1029" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1029" s="1" t="b">
         <v>0</v>
       </c>
@@ -51979,7 +51985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1034" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1034" s="1" t="b">
         <v>0</v>
       </c>
@@ -52023,7 +52029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1035" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1035" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1035" s="1" t="b">
         <v>0</v>
       </c>
@@ -52067,7 +52073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1036" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1036" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1036" s="1" t="b">
         <v>0</v>
       </c>
@@ -52111,7 +52117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1037" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1037" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1037" s="1" t="b">
         <v>0</v>
       </c>
@@ -52199,7 +52205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1039" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1039" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1039" s="1" t="b">
         <v>0</v>
       </c>
@@ -52243,7 +52249,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1040" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1040" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1040" s="1" t="b">
         <v>0</v>
       </c>
@@ -52287,7 +52293,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1041" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1041" s="1" t="b">
         <v>0</v>
       </c>
@@ -52331,7 +52337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1042" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1042" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1042" s="1" t="b">
         <v>0</v>
       </c>
@@ -52375,7 +52381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1043" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1043" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1043" s="1" t="b">
         <v>0</v>
       </c>
@@ -52419,7 +52425,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1044" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1044" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1044" s="1" t="b">
         <v>0</v>
       </c>
@@ -52463,7 +52469,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1045" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1045" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1045" s="1" t="b">
         <v>0</v>
       </c>
@@ -52551,7 +52557,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1047" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1047" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1047" s="1" t="b">
         <v>0</v>
       </c>
@@ -52595,7 +52601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1048" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1048" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048" s="1" t="b">
         <v>0</v>
       </c>
@@ -52727,7 +52733,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1051" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1051" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1051" s="1" t="b">
         <v>0</v>
       </c>
@@ -52771,7 +52777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1052" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1052" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1052" s="1" t="b">
         <v>0</v>
       </c>
@@ -52815,7 +52821,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1053" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1053" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1053" s="1" t="b">
         <v>0</v>
       </c>
@@ -52859,7 +52865,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1054" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1054" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1054" s="1" t="b">
         <v>0</v>
       </c>
@@ -52991,7 +52997,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1057" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1057" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1057" s="1" t="b">
         <v>0</v>
       </c>
@@ -53037,7 +53043,7 @@
     </row>
     <row r="1058" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1058" s="6" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B1058" s="3">
         <v>352020</v>
@@ -53079,7 +53085,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1059" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1059" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1059" s="1" t="b">
         <v>0</v>
       </c>
@@ -53123,7 +53129,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1060" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1060" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1060" s="1" t="b">
         <v>0</v>
       </c>
@@ -53167,7 +53173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1061" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1061" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1061" s="1" t="b">
         <v>0</v>
       </c>
@@ -53211,7 +53217,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1062" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1062" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1062" s="1" t="b">
         <v>0</v>
       </c>
@@ -53255,7 +53261,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1063" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1063" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1063" s="1" t="b">
         <v>0</v>
       </c>
@@ -53299,7 +53305,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1064" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1064" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1064" s="1" t="b">
         <v>0</v>
       </c>
@@ -53387,7 +53393,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1066" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1066" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1066" s="1" t="b">
         <v>0</v>
       </c>
@@ -53431,7 +53437,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1067" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1067" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1067" s="1" t="b">
         <v>0</v>
       </c>
@@ -53609,13 +53615,13 @@
     </row>
     <row r="1071" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="5" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B1071" s="3">
         <v>353010</v>
       </c>
       <c r="C1071" s="1" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="D1071" s="1" t="s">
         <v>1577</v>
@@ -53653,7 +53659,7 @@
     </row>
     <row r="1072" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B1072" s="3">
         <v>353010</v>
@@ -53697,7 +53703,7 @@
     </row>
     <row r="1073" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="5" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B1073" s="3">
         <v>353010</v>
@@ -53785,7 +53791,7 @@
     </row>
     <row r="1075" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1075" s="6" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B1075" s="3">
         <v>353020</v>
@@ -53873,7 +53879,7 @@
     </row>
     <row r="1077" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1077" s="5" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B1077" s="3">
         <v>353040</v>
@@ -53917,7 +53923,7 @@
     </row>
     <row r="1078" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1078" s="5" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B1078" s="3">
         <v>353050</v>
@@ -53961,7 +53967,7 @@
     </row>
     <row r="1079" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1079" s="6" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B1079" s="3">
         <v>353060</v>
@@ -54005,7 +54011,7 @@
     </row>
     <row r="1080" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1080" s="6" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B1080" s="3">
         <v>353060</v>
@@ -54311,7 +54317,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1087" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1087" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1087" s="1" t="b">
         <v>0</v>
       </c>
@@ -54355,7 +54361,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1088" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1088" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1088" s="1" t="b">
         <v>0</v>
       </c>
@@ -54399,7 +54405,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1089" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1089" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1089" s="1" t="b">
         <v>0</v>
       </c>
@@ -54443,7 +54449,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1090" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1090" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1090" s="1" t="b">
         <v>0</v>
       </c>
@@ -54487,7 +54493,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1091" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1091" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1091" s="1" t="b">
         <v>0</v>
       </c>
@@ -54531,7 +54537,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1092" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1092" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1092" s="1" t="b">
         <v>0</v>
       </c>
@@ -54575,7 +54581,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1093" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1093" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1093" s="1" t="b">
         <v>0</v>
       </c>
@@ -54619,7 +54625,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1094" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1094" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1094" s="1" t="b">
         <v>0</v>
       </c>
@@ -54663,7 +54669,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1095" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1095" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1095" s="1" t="b">
         <v>0</v>
       </c>
@@ -54795,7 +54801,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1098" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1098" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1098" s="1" t="b">
         <v>0</v>
       </c>
@@ -54839,7 +54845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1099" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1099" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1099" s="1" t="b">
         <v>0</v>
       </c>
@@ -54883,7 +54889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1100" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1100" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1100" s="1" t="b">
         <v>0</v>
       </c>
@@ -54927,7 +54933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1101" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1101" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1101" s="1" t="b">
         <v>0</v>
       </c>
@@ -54971,7 +54977,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1102" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1102" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1102" s="1" t="b">
         <v>0</v>
       </c>
@@ -55015,7 +55021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1103" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1103" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1103" s="1" t="b">
         <v>0</v>
       </c>
@@ -55059,7 +55065,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1104" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1104" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1104" s="1" t="b">
         <v>0</v>
       </c>
@@ -55103,7 +55109,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1105" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1105" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1105" s="1" t="b">
         <v>0</v>
       </c>
@@ -55147,7 +55153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1106" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1106" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1106" s="1" t="b">
         <v>0</v>
       </c>
@@ -55191,7 +55197,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1107" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1107" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1107" s="1" t="b">
         <v>0</v>
       </c>
@@ -55235,7 +55241,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1108" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1108" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1108" s="1" t="b">
         <v>0</v>
       </c>
@@ -55279,7 +55285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1109" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1109" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1109" s="1" t="b">
         <v>0</v>
       </c>
@@ -55323,7 +55329,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1110" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1110" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1110" s="1" t="b">
         <v>0</v>
       </c>
@@ -55367,7 +55373,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1111" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1111" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1111" s="1" t="b">
         <v>0</v>
       </c>
@@ -55455,7 +55461,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1113" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1113" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1113" s="1" t="b">
         <v>0</v>
       </c>
@@ -55499,7 +55505,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1114" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1114" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1114" s="1" t="b">
         <v>0</v>
       </c>
@@ -55543,7 +55549,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1115" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1115" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1115" s="1" t="b">
         <v>0</v>
       </c>
@@ -55587,7 +55593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1116" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1116" s="1" t="b">
         <v>0</v>
       </c>
@@ -55631,7 +55637,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1117" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1117" s="1" t="b">
         <v>0</v>
       </c>
@@ -55675,7 +55681,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1118" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1118" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1118" s="1" t="b">
         <v>0</v>
       </c>
@@ -55719,7 +55725,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1119" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1119" s="1" t="b">
         <v>0</v>
       </c>
@@ -55763,7 +55769,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1120" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1120" s="1" t="b">
         <v>0</v>
       </c>
@@ -55807,7 +55813,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1121" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1121" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1121" s="1" t="b">
         <v>0</v>
       </c>
@@ -56687,7 +56693,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1141" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1141" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1141" s="1" t="b">
         <v>0</v>
       </c>
@@ -56731,7 +56737,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1142" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1142" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1142" s="1" t="b">
         <v>0</v>
       </c>
@@ -56775,7 +56781,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1143" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1143" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1143" s="1" t="b">
         <v>0</v>
       </c>
@@ -56819,7 +56825,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1144" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1144" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1144" s="1" t="b">
         <v>0</v>
       </c>
@@ -56863,7 +56869,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1145" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1145" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1145" s="1" t="b">
         <v>0</v>
       </c>
@@ -56907,7 +56913,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1146" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1146" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1146" s="1" t="b">
         <v>0</v>
       </c>
@@ -56951,7 +56957,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1147" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1147" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1147" s="1" t="b">
         <v>0</v>
       </c>
@@ -56995,7 +57001,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1148" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1148" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1148" s="1" t="b">
         <v>0</v>
       </c>
@@ -57039,7 +57045,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1149" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1149" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1149" s="1" t="b">
         <v>0</v>
       </c>
@@ -57479,7 +57485,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1159" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1159" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1159" s="1" t="b">
         <v>0</v>
       </c>
@@ -57523,7 +57529,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1160" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1160" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1160" s="1" t="b">
         <v>0</v>
       </c>
@@ -57567,7 +57573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1161" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1161" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1161" s="1" t="b">
         <v>0</v>
       </c>
@@ -57611,7 +57617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1162" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1162" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1162" s="1" t="b">
         <v>0</v>
       </c>
@@ -57655,7 +57661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1163" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1163" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1163" s="1" t="b">
         <v>0</v>
       </c>
@@ -57699,7 +57705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1164" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1164" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1164" s="1" t="b">
         <v>0</v>
       </c>
@@ -57743,7 +57749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1165" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1165" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1165" s="1" t="b">
         <v>0</v>
       </c>
@@ -57787,7 +57793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1166" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1166" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1166" s="1" t="b">
         <v>0</v>
       </c>
@@ -57831,7 +57837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1167" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1167" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1167" s="1" t="b">
         <v>0</v>
       </c>
@@ -57875,7 +57881,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1168" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1168" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1168" s="1" t="b">
         <v>0</v>
       </c>
@@ -57919,7 +57925,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1169" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1169" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1169" s="1" t="b">
         <v>0</v>
       </c>
@@ -57963,7 +57969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1170" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1170" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="1" t="b">
         <v>0</v>
       </c>
@@ -58007,7 +58013,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1171" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1171" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1171" s="1" t="b">
         <v>0</v>
       </c>
@@ -58051,7 +58057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1172" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1172" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="1" t="b">
         <v>0</v>
       </c>
@@ -58095,7 +58101,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1173" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1173" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1173" s="1" t="b">
         <v>0</v>
       </c>
@@ -58139,7 +58145,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1174" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1174" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="1" t="b">
         <v>0</v>
       </c>
@@ -58183,7 +58189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1175" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1175" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1175" s="1" t="b">
         <v>0</v>
       </c>
@@ -58227,7 +58233,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1176" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1176" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="1" t="b">
         <v>0</v>
       </c>
@@ -58271,7 +58277,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1177" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1177" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1177" s="1" t="b">
         <v>0</v>
       </c>
@@ -58315,7 +58321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1178" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1178" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1178" s="1" t="b">
         <v>0</v>
       </c>
@@ -58359,7 +58365,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1179" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1179" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1179" s="1" t="b">
         <v>0</v>
       </c>
@@ -58403,7 +58409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1180" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1180" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1180" s="1" t="b">
         <v>0</v>
       </c>
@@ -58447,7 +58453,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1181" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1181" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1181" s="1" t="b">
         <v>0</v>
       </c>
@@ -58491,7 +58497,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1182" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1182" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1182" s="1" t="b">
         <v>0</v>
       </c>
@@ -58535,7 +58541,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1183" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1183" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="1" t="b">
         <v>0</v>
       </c>
@@ -58579,7 +58585,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1184" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1184" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="1" t="b">
         <v>0</v>
       </c>
@@ -58623,7 +58629,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1185" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1185" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1185" s="1" t="b">
         <v>0</v>
       </c>
@@ -58667,7 +58673,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1186" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1186" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1186" s="1" t="b">
         <v>0</v>
       </c>
@@ -58711,7 +58717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1187" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1187" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1187" s="1" t="b">
         <v>0</v>
       </c>
@@ -58755,7 +58761,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1188" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1188" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="1" t="b">
         <v>0</v>
       </c>
@@ -58799,7 +58805,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1189" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1189" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1189" s="1" t="b">
         <v>0</v>
       </c>
@@ -58843,7 +58849,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1190" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1190" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1190" s="1" t="b">
         <v>0</v>
       </c>
@@ -58887,7 +58893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1191" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1191" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1191" s="1" t="b">
         <v>0</v>
       </c>
@@ -58931,7 +58937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1192" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1192" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1192" s="1" t="b">
         <v>0</v>
       </c>
@@ -58975,7 +58981,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1193" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1193" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1193" s="1" t="b">
         <v>0</v>
       </c>
@@ -59019,7 +59025,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1194" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1194" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1194" s="1" t="b">
         <v>0</v>
       </c>
@@ -59063,7 +59069,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1195" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1195" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1195" s="1" t="b">
         <v>0</v>
       </c>
@@ -59107,7 +59113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1196" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1196" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1196" s="1" t="b">
         <v>0</v>
       </c>
@@ -59151,7 +59157,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1197" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1197" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1197" s="1" t="b">
         <v>0</v>
       </c>
@@ -59195,7 +59201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1198" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1198" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1198" s="1" t="b">
         <v>0</v>
       </c>
@@ -59239,7 +59245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1199" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1199" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1199" s="1" t="b">
         <v>0</v>
       </c>
@@ -59283,7 +59289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1200" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1200" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1200" s="1" t="b">
         <v>0</v>
       </c>
@@ -59327,7 +59333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1201" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1201" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1201" s="1" t="b">
         <v>0</v>
       </c>
@@ -59371,7 +59377,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1202" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1202" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1202" s="1" t="b">
         <v>0</v>
       </c>
@@ -59415,7 +59421,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1203" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1203" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1203" s="1" t="b">
         <v>0</v>
       </c>
@@ -59459,7 +59465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1204" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1204" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1204" s="1" t="b">
         <v>0</v>
       </c>
@@ -59503,7 +59509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1205" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1205" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1205" s="1" t="b">
         <v>0</v>
       </c>
@@ -59547,7 +59553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1206" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1206" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1206" s="1" t="b">
         <v>0</v>
       </c>
@@ -59591,7 +59597,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1207" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1207" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1207" s="1" t="b">
         <v>0</v>
       </c>
@@ -59635,7 +59641,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1208" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1208" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1208" s="1" t="b">
         <v>0</v>
       </c>
@@ -59679,7 +59685,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1209" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1209" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1209" s="1" t="b">
         <v>0</v>
       </c>
@@ -59723,7 +59729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1210" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1210" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1210" s="1" t="b">
         <v>0</v>
       </c>
@@ -59767,7 +59773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1211" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1211" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1211" s="1" t="b">
         <v>0</v>
       </c>
@@ -59811,7 +59817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1212" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1212" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1212" s="1" t="b">
         <v>0</v>
       </c>
@@ -59855,7 +59861,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1213" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1213" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1213" s="1" t="b">
         <v>0</v>
       </c>
@@ -59899,7 +59905,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1214" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1214" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1214" s="1" t="b">
         <v>0</v>
       </c>
@@ -59943,7 +59949,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1215" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1215" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1215" s="1" t="b">
         <v>0</v>
       </c>
@@ -59987,7 +59993,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1216" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1216" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1216" s="1" t="b">
         <v>0</v>
       </c>
@@ -60031,7 +60037,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1217" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1217" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1217" s="1" t="b">
         <v>0</v>
       </c>
@@ -60075,7 +60081,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1218" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1218" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1218" s="1" t="b">
         <v>0</v>
       </c>
@@ -60119,7 +60125,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1219" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1219" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1219" s="1" t="b">
         <v>0</v>
       </c>
@@ -60163,7 +60169,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1220" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1220" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1220" s="1" t="b">
         <v>0</v>
       </c>
@@ -60207,7 +60213,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1221" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1221" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1221" s="1" t="b">
         <v>0</v>
       </c>
@@ -60251,7 +60257,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1222" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1222" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1222" s="1" t="b">
         <v>0</v>
       </c>
@@ -60295,7 +60301,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1223" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1223" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1223" s="1" t="b">
         <v>0</v>
       </c>
@@ -60339,7 +60345,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1224" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1224" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1224" s="1" t="b">
         <v>0</v>
       </c>
@@ -60383,7 +60389,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1225" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1225" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1225" s="1" t="b">
         <v>0</v>
       </c>
@@ -60427,7 +60433,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1226" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1226" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1226" s="1" t="b">
         <v>0</v>
       </c>
@@ -60471,9 +60477,9 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1227" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1227" s="1" t="b">
-        <v>0</v>
+    <row r="1227" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1227" s="6" t="s">
+        <v>2013</v>
       </c>
       <c r="B1227" s="3">
         <v>360150</v>
@@ -60515,7 +60521,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1228" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1228" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1228" s="1" t="b">
         <v>0</v>
       </c>
@@ -60559,7 +60565,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1229" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1229" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1229" s="1" t="b">
         <v>0</v>
       </c>
@@ -60603,7 +60609,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="1230" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1230" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1230" s="1" t="b">
         <v>0</v>
       </c>
@@ -60647,7 +60653,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1231" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1231" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1231" s="1" t="b">
         <v>0</v>
       </c>
@@ -60691,7 +60697,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1232" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1232" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1232" s="1" t="b">
         <v>0</v>
       </c>
@@ -60735,7 +60741,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1233" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1233" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1233" s="1" t="b">
         <v>0</v>
       </c>
@@ -60779,7 +60785,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1234" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1234" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1234" s="1" t="b">
         <v>0</v>
       </c>
@@ -60823,7 +60829,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1235" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1235" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1235" s="1" t="b">
         <v>0</v>
       </c>
@@ -60911,7 +60917,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1237" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1237" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1237" s="1" t="b">
         <v>0</v>
       </c>
@@ -60955,7 +60961,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1238" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1238" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1238" s="1" t="b">
         <v>0</v>
       </c>
@@ -60999,7 +61005,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1239" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1239" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1239" s="1" t="b">
         <v>0</v>
       </c>
@@ -61043,7 +61049,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1240" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1240" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1240" s="1" t="b">
         <v>0</v>
       </c>
@@ -61087,7 +61093,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1241" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1241" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1241" s="1" t="b">
         <v>0</v>
       </c>
@@ -61131,7 +61137,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1242" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1242" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1242" s="1" t="b">
         <v>0</v>
       </c>
@@ -61175,7 +61181,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1243" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1243" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1243" s="1" t="b">
         <v>0</v>
       </c>
@@ -61219,7 +61225,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1244" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1244" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1244" s="1" t="b">
         <v>0</v>
       </c>
@@ -61263,7 +61269,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1245" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1245" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1245" s="1" t="b">
         <v>0</v>
       </c>
@@ -61307,7 +61313,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1246" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1246" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1246" s="1" t="b">
         <v>0</v>
       </c>
@@ -61351,7 +61357,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1247" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1247" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1247" s="1" t="b">
         <v>0</v>
       </c>
@@ -61395,7 +61401,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1248" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1248" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1248" s="1" t="b">
         <v>0</v>
       </c>
@@ -61439,7 +61445,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1249" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1249" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="1" t="b">
         <v>0</v>
       </c>
@@ -61483,7 +61489,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1250" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1250" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1250" s="1" t="b">
         <v>0</v>
       </c>
@@ -61527,7 +61533,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1251" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1251" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="1" t="b">
         <v>0</v>
       </c>
@@ -61571,7 +61577,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1252" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1252" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1252" s="1" t="b">
         <v>0</v>
       </c>
@@ -61615,7 +61621,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1253" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1253" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1253" s="1" t="b">
         <v>0</v>
       </c>
@@ -61659,7 +61665,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1254" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1254" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1254" s="1" t="b">
         <v>0</v>
       </c>
@@ -61703,7 +61709,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1255" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1255" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1255" s="1" t="b">
         <v>0</v>
       </c>
@@ -61747,7 +61753,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1256" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1256" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1256" s="1" t="b">
         <v>0</v>
       </c>
@@ -61791,7 +61797,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1257" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1257" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1257" s="1" t="b">
         <v>0</v>
       </c>
@@ -61835,7 +61841,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1258" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1258" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1258" s="1" t="b">
         <v>0</v>
       </c>
@@ -61879,7 +61885,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1259" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1259" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1259" s="1" t="b">
         <v>0</v>
       </c>
@@ -61923,7 +61929,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1260" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1260" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1260" s="1" t="b">
         <v>0</v>
       </c>
@@ -61967,7 +61973,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1261" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1261" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1261" s="1" t="b">
         <v>0</v>
       </c>
@@ -62011,7 +62017,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1262" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1262" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1262" s="1" t="b">
         <v>0</v>
       </c>
@@ -62055,7 +62061,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1263" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1263" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1263" s="1" t="b">
         <v>0</v>
       </c>
@@ -62099,7 +62105,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1264" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1264" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1264" s="1" t="b">
         <v>0</v>
       </c>
@@ -62143,7 +62149,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1265" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1265" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1265" s="1" t="b">
         <v>0</v>
       </c>
@@ -62187,7 +62193,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1266" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1266" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1266" s="1" t="b">
         <v>0</v>
       </c>
@@ -62231,7 +62237,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1267" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1267" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1267" s="1" t="b">
         <v>0</v>
       </c>
@@ -62275,7 +62281,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="1268" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1268" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1268" s="1" t="b">
         <v>0</v>
       </c>
@@ -62319,7 +62325,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1269" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1269" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1269" s="1" t="b">
         <v>0</v>
       </c>
@@ -62363,7 +62369,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1270" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1270" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1270" s="1" t="b">
         <v>0</v>
       </c>
@@ -62451,7 +62457,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1272" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1272" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1272" s="1" t="b">
         <v>0</v>
       </c>
@@ -62495,7 +62501,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1273" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1273" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1273" s="1" t="b">
         <v>0</v>
       </c>
@@ -62539,7 +62545,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1274" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1274" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1274" s="1" t="b">
         <v>0</v>
       </c>
@@ -62583,7 +62589,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1275" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1275" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1275" s="1" t="b">
         <v>0</v>
       </c>
@@ -62627,7 +62633,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1276" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1276" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1276" s="1" t="b">
         <v>0</v>
       </c>
@@ -62671,7 +62677,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1277" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1277" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1277" s="1" t="b">
         <v>0</v>
       </c>
@@ -62715,7 +62721,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1278" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1278" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1278" s="1" t="b">
         <v>0</v>
       </c>
@@ -62759,7 +62765,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1279" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1279" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1279" s="1" t="b">
         <v>0</v>
       </c>
@@ -62803,7 +62809,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1280" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1280" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1280" s="1" t="b">
         <v>0</v>
       </c>
@@ -62849,7 +62855,7 @@
     </row>
     <row r="1281" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1281" s="6" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B1281" s="3">
         <v>383010</v>
@@ -62979,7 +62985,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="1284" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1284" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1284" s="1" t="b">
         <v>0</v>
       </c>
@@ -63023,7 +63029,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="1285" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1285" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1285" s="1" t="b">
         <v>0</v>
       </c>
@@ -63067,7 +63073,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="1286" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1286" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1286" s="1" t="b">
         <v>0</v>
       </c>
@@ -63199,7 +63205,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="1289" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1289" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1289" s="1" t="b">
         <v>0</v>
       </c>
@@ -63287,7 +63293,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1291" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1291" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1291" s="1" t="b">
         <v>0</v>
       </c>
@@ -63419,7 +63425,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1294" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1294" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1294" s="1" t="b">
         <v>0</v>
       </c>
@@ -63463,7 +63469,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1295" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1295" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1295" s="1" t="b">
         <v>0</v>
       </c>
@@ -63507,7 +63513,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1296" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1296" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1296" s="1" t="b">
         <v>0</v>
       </c>
@@ -63551,7 +63557,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1297" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1297" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1297" s="1" t="b">
         <v>0</v>
       </c>
@@ -63595,7 +63601,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="1298" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1298" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1298" s="1" t="b">
         <v>0</v>
       </c>
@@ -63639,7 +63645,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1299" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1299" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1299" s="1" t="b">
         <v>0</v>
       </c>
@@ -63683,7 +63689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1300" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1300" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1300" s="1" t="b">
         <v>0</v>
       </c>
@@ -63727,7 +63733,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="1301" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1301" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1301" s="1" t="b">
         <v>0</v>
       </c>
@@ -63817,7 +63823,7 @@
     </row>
     <row r="1303" spans="1:14" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B1303" s="3">
         <v>390021</v>
@@ -66019,7 +66025,7 @@
     <hyperlink ref="A29" r:id="rId1315" xr:uid="{EF69FC41-0BD7-254A-BA36-9583AA729450}"/>
     <hyperlink ref="A15" r:id="rId1316" xr:uid="{80C3CDE4-F5C1-7F43-A09B-68F5B82682C2}"/>
     <hyperlink ref="A12" r:id="rId1317" xr:uid="{370D853C-B721-744F-B56C-216D96067C1B}"/>
-    <hyperlink ref="A17" r:id="rId1318" xr:uid="{FDF3E881-F3B1-EF4C-9AB5-4B51775CDCF8}"/>
+    <hyperlink ref="A17" r:id="rId1318" display="http://149.165.154.65/data/HDF5EOS/Etna/miaplpy" xr:uid="{FDF3E881-F3B1-EF4C-9AB5-4B51775CDCF8}"/>
     <hyperlink ref="B16" r:id="rId1319" display="https://volcano.si.edu/volcano.cfm?vn=211060" xr:uid="{6404AF50-EF75-3F4D-9F4B-F3C1376D48F0}"/>
     <hyperlink ref="A16" r:id="rId1320" xr:uid="{72ED6A20-3786-6443-9A91-4E4CD0368F13}"/>
     <hyperlink ref="B24" r:id="rId1321" display="https://volcano.si.edu/volcano.cfm?vn=212050" xr:uid="{7A7479CF-FF5D-384F-8B18-CCD520E95C55}"/>
@@ -66058,6 +66064,8 @@
     <hyperlink ref="A459" r:id="rId1354" location="/?minScale=-2&amp;maxScale=2" xr:uid="{979264A1-1EDE-9941-B821-5E19B7EC19AE}"/>
     <hyperlink ref="A338" r:id="rId1355" location="/?minScale=-5&amp;maxScale=5&amp;background=satellite" xr:uid="{B59A7083-C90A-3442-B482-B97C567E58E3}"/>
     <hyperlink ref="A385" r:id="rId1356" location="/?minScale=-2&amp;maxScale=2" xr:uid="{ADDB8508-D649-ED42-98CC-A33FD8E3B0DE}"/>
+    <hyperlink ref="A972" r:id="rId1357" location="/?minScale=-5&amp;maxScale=5&amp;background=hillshade&amp;contour=true" xr:uid="{E51DAFBE-CC96-0342-B090-626EFF110157}"/>
+    <hyperlink ref="A1227" r:id="rId1358" location="/?minScale=-3&amp;maxScale=3" xr:uid="{B3D66DE3-C82E-9A45-8E9F-7C69CBF97669}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/tools/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFA7C93-7004-2940-B3FC-9FF8478A2B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF17D1A-AEFA-5046-B9EA-C53C0872F219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5660" yWindow="660" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
+    <workbookView xWindow="940" yWindow="660" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14654,7 +14654,7 @@
     </row>
     <row r="186" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B186" s="3">
         <v>233010</v>

--- a/Holocene_Volcanoes_volcdef_cfg.xlsx
+++ b/Holocene_Volcanoes_volcdef_cfg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/famelung/code/minsar/tools/webconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF17D1A-AEFA-5046-B9EA-C53C0872F219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3BC866-88F5-B94D-AEB4-59967A799348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="660" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
+    <workbookView xWindow="3120" yWindow="4460" windowWidth="33620" windowHeight="19280" xr2:uid="{C0385577-DB88-5B46-BC32-5548AF298521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61734,7 +61734,7 @@
     </row>
     <row r="1256" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1256" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1256" s="3">
         <v>373080</v>
